--- a/excel/KeystoneBenefitTech_PL_Model.xlsx
+++ b/excel/KeystoneBenefitTech_PL_Model.xlsx
@@ -42,7 +42,7 @@
     <numFmt numFmtId="167" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="168" formatCode="$#,##0.0&quot;K&quot;"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -205,8 +205,38 @@
       <color rgb="00161616"/>
       <sz val="10"/>
     </font>
+    <font/>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="004B9BCB"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000B4779"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00112E51"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00999999"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00161616"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -285,8 +315,14 @@
         <bgColor rgb="00BFF18C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4FD"/>
+        <bgColor rgb="00E8F4FD"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -351,11 +387,91 @@
         <color rgb="000B4779"/>
       </bottom>
     </border>
+    <border>
+      <right/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="000B4779"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="000B4779"/>
+      </right>
+      <top style="medium">
+        <color rgb="000B4779"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="000B4779"/>
+      </right>
+      <top style="medium">
+        <color rgb="000B4779"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="000B4779"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="004B9BCB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="004B9BCB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="004B9BCB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="004B9BCB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="004B9BCB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="000B4779"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -546,6 +662,48 @@
     <xf numFmtId="0" fontId="25" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="8" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -702,6 +860,2161 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Revenue vs Cost of Revenue — Monthly</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1200" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Revenue</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$B$50:$M$50</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$B$51:$M$51</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Cost of Revenue</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2BCCD3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2BCCD3"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$B$52:$M$52</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="161616"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>$K</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="$#,##0.0&quot;K&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="161616"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0">
+            <a:solidFill>
+              <a:srgbClr val="161616"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Contribution Margin % — Monthly Trend</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1200" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Contribution Margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$B$50:$M$50</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$B$54:$M$54</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="161616"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Margin %</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="161616"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0">
+            <a:solidFill>
+              <a:srgbClr val="161616"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Expense Breakdown by Department — Full Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1200" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Expense by Department</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2BCCD3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="BFF18C"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4B9BCB"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="E8833A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="112E51"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1A8A8A"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="800" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="161616"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="800" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="161616"/>
+                  </a:solidFill>
+                  <a:latin typeface="Arial"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <showVal val="0"/>
+            <showCatName val="1"/>
+            <showPercent val="1"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$59:$A$65</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$N$59:$N$65</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0">
+            <a:solidFill>
+              <a:srgbClr val="161616"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Monthly Revenue by Product — FY2025</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1200" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!B82</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$83:$A$94</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$B$83:$B$94</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!C82</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2BCCD3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2BCCD3"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$83:$A$94</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$C$83:$C$94</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!D82</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="BFF18C"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="BFF18C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$83:$A$94</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$D$83:$D$94</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!E82</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4B9BCB"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="4B9BCB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$83:$A$94</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$E$83:$E$94</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="161616"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Revenue ($K)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="$#,##0.0&quot;K&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="161616"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0">
+            <a:solidFill>
+              <a:srgbClr val="161616"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Contribution Margin % by Product — FY2025</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1200" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!B96</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$97:$A$108</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$B$97:$B$108</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!C96</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2BCCD3"/>
+            </a:solidFill>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="2BCCD3"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$97:$A$108</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$C$97:$C$108</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!D96</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="BFF18C"/>
+            </a:solidFill>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="BFF18C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$97:$A$108</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$D$97:$D$108</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!E96</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4B9BCB"/>
+            </a:solidFill>
+            <a:ln w="28000">
+              <a:solidFill>
+                <a:srgbClr val="4B9BCB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$97:$A$108</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$E$97:$E$108</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="161616"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Margin %</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="161616"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0">
+            <a:solidFill>
+              <a:srgbClr val="161616"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Full Year Revenue Mix — FY2025</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1200" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Revenue Share</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="2BCCD3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="BFF18C"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="4B9BCB"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <txPr>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0">
+                    <a:solidFill>
+                      <a:srgbClr val="161616"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr sz="900" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="161616"/>
+                  </a:solidFill>
+                  <a:latin typeface="Arial"/>
+                </a:endParaRPr>
+              </a:p>
+            </txPr>
+            <showVal val="0"/>
+            <showCatName val="1"/>
+            <showPercent val="1"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$68:$A$71</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$B$68:$B$71</f>
+            </numRef>
+          </val>
+        </ser>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0">
+            <a:solidFill>
+              <a:srgbClr val="161616"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Revenue vs Cost of Revenue vs Contribution Margin — FY2025</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1200" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!B110</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$111:$A$114</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$B$111:$B$114</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!C110</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2BCCD3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2BCCD3"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$111:$A$114</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$C$111:$C$114</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!D110</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="BFF18C"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="BFF18C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$111:$A$114</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$D$111:$D$114</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="161616"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>$K</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="$#,##0.0&quot;K&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="161616"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0">
+            <a:solidFill>
+              <a:srgbClr val="161616"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Department Cost Distribution by Product — FY2025</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="1">
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1200" b="1">
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!B73</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="0B4779"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="0B4779"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$74:$A$80</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$B$74:$B$80</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!C73</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2BCCD3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2BCCD3"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$74:$A$80</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$C$74:$C$80</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!D73</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="BFF18C"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="BFF18C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$74:$A$80</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$D$74:$D$80</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Charts &amp; Visuals'!E73</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4B9BCB"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="4B9BCB"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$A$74:$A$80</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts &amp; Visuals'!$E$74:$E$80</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="161616"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>$K</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="$#,##0.0&quot;K&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <txPr>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0">
+                <a:solidFill>
+                  <a:srgbClr val="161616"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="800" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:endParaRPr>
+          </a:p>
+        </txPr>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0">
+              <a:solidFill>
+                <a:srgbClr val="161616"/>
+              </a:solidFill>
+              <a:latin typeface="Arial"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="900" b="0">
+            <a:solidFill>
+              <a:srgbClr val="161616"/>
+            </a:solidFill>
+            <a:latin typeface="Arial"/>
+          </a:endParaRPr>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln>
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>80</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>97</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>117</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="7" name="Chart 7"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>134</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="8" name="Chart 8"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -17835,7 +20148,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -18569,7 +20881,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -19303,7 +21614,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -20648,60 +22958,3517 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000B4779"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:T159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="89" t="inlineStr">
         <is>
           <t>Keystone BenefitTech, Inc.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="44" t="inlineStr">
-        <is>
-          <t>Charts &amp; Visuals</t>
-        </is>
-      </c>
-      <c r="H2" s="43" t="inlineStr">
+      <c r="A2" s="90" t="inlineStr">
+        <is>
+          <t>Charts &amp; Visuals — FY2025</t>
+        </is>
+      </c>
+      <c r="H2" s="91" t="inlineStr">
         <is>
           <t>Last Updated: 2026-02-28</t>
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="92" t="n"/>
+      <c r="B3" s="92" t="n"/>
+      <c r="C3" s="92" t="n"/>
+      <c r="D3" s="92" t="n"/>
+      <c r="E3" s="92" t="n"/>
+      <c r="F3" s="92" t="n"/>
+      <c r="G3" s="92" t="n"/>
+      <c r="H3" s="92" t="n"/>
+      <c r="I3" s="92" t="n"/>
+      <c r="J3" s="92" t="n"/>
+      <c r="K3" s="92" t="n"/>
+      <c r="L3" s="93" t="n"/>
+      <c r="M3" s="93" t="n"/>
+      <c r="N3" s="93" t="n"/>
+      <c r="O3" s="93" t="n"/>
+      <c r="P3" s="93" t="n"/>
+      <c r="Q3" s="93" t="n"/>
+      <c r="R3" s="93" t="n"/>
+      <c r="S3" s="93" t="n"/>
+      <c r="T3" s="93" t="n"/>
+    </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="77" t="inlineStr">
-        <is>
-          <t>Charts &amp; Visuals — FY2025 — Under Construction</t>
-        </is>
-      </c>
-      <c r="B4" s="78" t="n"/>
-      <c r="C4" s="78" t="n"/>
-      <c r="D4" s="78" t="n"/>
-      <c r="E4" s="78" t="n"/>
-      <c r="F4" s="78" t="n"/>
-      <c r="G4" s="78" t="n"/>
-      <c r="H4" s="78" t="n"/>
+      <c r="A4" s="92" t="n"/>
+      <c r="B4" s="92" t="n"/>
+      <c r="C4" s="92" t="n"/>
+      <c r="D4" s="92" t="n"/>
+      <c r="E4" s="92" t="n"/>
+      <c r="F4" s="92" t="n"/>
+      <c r="G4" s="92" t="n"/>
+      <c r="H4" s="92" t="n"/>
+      <c r="I4" s="92" t="n"/>
+      <c r="J4" s="92" t="n"/>
+      <c r="K4" s="92" t="n"/>
+      <c r="L4" s="93" t="n"/>
+      <c r="M4" s="93" t="n"/>
+      <c r="N4" s="93" t="n"/>
+      <c r="O4" s="93" t="n"/>
+      <c r="P4" s="93" t="n"/>
+      <c r="Q4" s="93" t="n"/>
+      <c r="R4" s="93" t="n"/>
+      <c r="S4" s="93" t="n"/>
+      <c r="T4" s="93" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="94" t="inlineStr">
+        <is>
+          <t>SELECT PRODUCT</t>
+        </is>
+      </c>
+      <c r="B5" s="95" t="n"/>
+      <c r="C5" s="95" t="n"/>
+      <c r="D5" s="95" t="n"/>
+      <c r="E5" s="95" t="n"/>
+      <c r="F5" s="95" t="n"/>
+      <c r="G5" s="95" t="n"/>
+      <c r="H5" s="95" t="n"/>
+      <c r="I5" s="96" t="n"/>
+      <c r="J5" s="96" t="n"/>
+      <c r="K5" s="96" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="97" t="inlineStr">
+        <is>
+          <t>Product:</t>
+        </is>
+      </c>
+      <c r="B6" s="98" t="inlineStr">
+        <is>
+          <t>iGO</t>
+        </is>
+      </c>
+      <c r="C6" s="99" t="inlineStr">
+        <is>
+          <t>← Select a product from the dropdown. Charts in Section 1 update automatically.</t>
+        </is>
+      </c>
+      <c r="D6" s="96" t="n"/>
+      <c r="E6" s="96" t="n"/>
+      <c r="F6" s="96" t="n"/>
+      <c r="G6" s="96" t="n"/>
+      <c r="H6" s="96" t="n"/>
+      <c r="I6" s="96" t="n"/>
+      <c r="J6" s="96" t="n"/>
+      <c r="K6" s="96" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="96" t="n"/>
+      <c r="B7" s="96" t="n"/>
+      <c r="C7" s="96" t="n"/>
+      <c r="D7" s="96" t="n"/>
+      <c r="E7" s="96" t="n"/>
+      <c r="F7" s="96" t="n"/>
+      <c r="G7" s="96" t="n"/>
+      <c r="H7" s="96" t="n"/>
+      <c r="I7" s="96" t="n"/>
+      <c r="J7" s="96" t="n"/>
+      <c r="K7" s="96" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="100" t="inlineStr">
+        <is>
+          <t>SECTION 1: SELECTED PRODUCT DASHBOARD</t>
+        </is>
+      </c>
+      <c r="B8" s="95" t="n"/>
+      <c r="C8" s="95" t="n"/>
+      <c r="D8" s="95" t="n"/>
+      <c r="E8" s="95" t="n"/>
+      <c r="F8" s="95" t="n"/>
+      <c r="G8" s="95" t="n"/>
+      <c r="H8" s="95" t="n"/>
+      <c r="I8" s="96" t="n"/>
+      <c r="J8" s="96" t="n"/>
+      <c r="K8" s="96" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="96" t="n"/>
+      <c r="B9" s="96" t="n"/>
+      <c r="C9" s="96" t="n"/>
+      <c r="D9" s="96" t="n"/>
+      <c r="E9" s="96" t="n"/>
+      <c r="F9" s="96" t="n"/>
+      <c r="G9" s="96" t="n"/>
+      <c r="H9" s="96" t="n"/>
+      <c r="I9" s="96" t="n"/>
+      <c r="J9" s="96" t="n"/>
+      <c r="K9" s="96" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="96" t="n"/>
+      <c r="B10" s="96" t="n"/>
+      <c r="C10" s="96" t="n"/>
+      <c r="D10" s="96" t="n"/>
+      <c r="E10" s="96" t="n"/>
+      <c r="F10" s="96" t="n"/>
+      <c r="G10" s="96" t="n"/>
+      <c r="H10" s="96" t="n"/>
+      <c r="I10" s="96" t="n"/>
+      <c r="J10" s="96" t="n"/>
+      <c r="K10" s="96" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="96" t="n"/>
+      <c r="B11" s="96" t="n"/>
+      <c r="C11" s="96" t="n"/>
+      <c r="D11" s="96" t="n"/>
+      <c r="E11" s="96" t="n"/>
+      <c r="F11" s="96" t="n"/>
+      <c r="G11" s="96" t="n"/>
+      <c r="H11" s="96" t="n"/>
+      <c r="I11" s="96" t="n"/>
+      <c r="J11" s="96" t="n"/>
+      <c r="K11" s="96" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="96" t="n"/>
+      <c r="B12" s="96" t="n"/>
+      <c r="C12" s="96" t="n"/>
+      <c r="D12" s="96" t="n"/>
+      <c r="E12" s="96" t="n"/>
+      <c r="F12" s="96" t="n"/>
+      <c r="G12" s="96" t="n"/>
+      <c r="H12" s="96" t="n"/>
+      <c r="I12" s="96" t="n"/>
+      <c r="J12" s="96" t="n"/>
+      <c r="K12" s="96" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="96" t="n"/>
+      <c r="B13" s="96" t="n"/>
+      <c r="C13" s="96" t="n"/>
+      <c r="D13" s="96" t="n"/>
+      <c r="E13" s="96" t="n"/>
+      <c r="F13" s="96" t="n"/>
+      <c r="G13" s="96" t="n"/>
+      <c r="H13" s="96" t="n"/>
+      <c r="I13" s="96" t="n"/>
+      <c r="J13" s="96" t="n"/>
+      <c r="K13" s="96" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="96" t="n"/>
+      <c r="B14" s="96" t="n"/>
+      <c r="C14" s="96" t="n"/>
+      <c r="D14" s="96" t="n"/>
+      <c r="E14" s="96" t="n"/>
+      <c r="F14" s="96" t="n"/>
+      <c r="G14" s="96" t="n"/>
+      <c r="H14" s="96" t="n"/>
+      <c r="I14" s="96" t="n"/>
+      <c r="J14" s="96" t="n"/>
+      <c r="K14" s="96" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="96" t="n"/>
+      <c r="B15" s="96" t="n"/>
+      <c r="C15" s="96" t="n"/>
+      <c r="D15" s="96" t="n"/>
+      <c r="E15" s="96" t="n"/>
+      <c r="F15" s="96" t="n"/>
+      <c r="G15" s="96" t="n"/>
+      <c r="H15" s="96" t="n"/>
+      <c r="I15" s="96" t="n"/>
+      <c r="J15" s="96" t="n"/>
+      <c r="K15" s="96" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="96" t="n"/>
+      <c r="B16" s="96" t="n"/>
+      <c r="C16" s="96" t="n"/>
+      <c r="D16" s="96" t="n"/>
+      <c r="E16" s="96" t="n"/>
+      <c r="F16" s="96" t="n"/>
+      <c r="G16" s="96" t="n"/>
+      <c r="H16" s="96" t="n"/>
+      <c r="I16" s="96" t="n"/>
+      <c r="J16" s="96" t="n"/>
+      <c r="K16" s="96" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="96" t="n"/>
+      <c r="B17" s="96" t="n"/>
+      <c r="C17" s="96" t="n"/>
+      <c r="D17" s="96" t="n"/>
+      <c r="E17" s="96" t="n"/>
+      <c r="F17" s="96" t="n"/>
+      <c r="G17" s="96" t="n"/>
+      <c r="H17" s="96" t="n"/>
+      <c r="I17" s="96" t="n"/>
+      <c r="J17" s="96" t="n"/>
+      <c r="K17" s="96" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="96" t="n"/>
+      <c r="B18" s="96" t="n"/>
+      <c r="C18" s="96" t="n"/>
+      <c r="D18" s="96" t="n"/>
+      <c r="E18" s="96" t="n"/>
+      <c r="F18" s="96" t="n"/>
+      <c r="G18" s="96" t="n"/>
+      <c r="H18" s="96" t="n"/>
+      <c r="I18" s="96" t="n"/>
+      <c r="J18" s="96" t="n"/>
+      <c r="K18" s="96" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="96" t="n"/>
+      <c r="B19" s="96" t="n"/>
+      <c r="C19" s="96" t="n"/>
+      <c r="D19" s="96" t="n"/>
+      <c r="E19" s="96" t="n"/>
+      <c r="F19" s="96" t="n"/>
+      <c r="G19" s="96" t="n"/>
+      <c r="H19" s="96" t="n"/>
+      <c r="I19" s="96" t="n"/>
+      <c r="J19" s="96" t="n"/>
+      <c r="K19" s="96" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="96" t="n"/>
+      <c r="B20" s="96" t="n"/>
+      <c r="C20" s="96" t="n"/>
+      <c r="D20" s="96" t="n"/>
+      <c r="E20" s="96" t="n"/>
+      <c r="F20" s="96" t="n"/>
+      <c r="G20" s="96" t="n"/>
+      <c r="H20" s="96" t="n"/>
+      <c r="I20" s="96" t="n"/>
+      <c r="J20" s="96" t="n"/>
+      <c r="K20" s="96" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="96" t="n"/>
+      <c r="B21" s="96" t="n"/>
+      <c r="C21" s="96" t="n"/>
+      <c r="D21" s="96" t="n"/>
+      <c r="E21" s="96" t="n"/>
+      <c r="F21" s="96" t="n"/>
+      <c r="G21" s="96" t="n"/>
+      <c r="H21" s="96" t="n"/>
+      <c r="I21" s="96" t="n"/>
+      <c r="J21" s="96" t="n"/>
+      <c r="K21" s="96" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="96" t="n"/>
+      <c r="B22" s="96" t="n"/>
+      <c r="C22" s="96" t="n"/>
+      <c r="D22" s="96" t="n"/>
+      <c r="E22" s="96" t="n"/>
+      <c r="F22" s="96" t="n"/>
+      <c r="G22" s="96" t="n"/>
+      <c r="H22" s="96" t="n"/>
+      <c r="I22" s="96" t="n"/>
+      <c r="J22" s="96" t="n"/>
+      <c r="K22" s="96" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="96" t="n"/>
+      <c r="B23" s="96" t="n"/>
+      <c r="C23" s="96" t="n"/>
+      <c r="D23" s="96" t="n"/>
+      <c r="E23" s="96" t="n"/>
+      <c r="F23" s="96" t="n"/>
+      <c r="G23" s="96" t="n"/>
+      <c r="H23" s="96" t="n"/>
+      <c r="I23" s="96" t="n"/>
+      <c r="J23" s="96" t="n"/>
+      <c r="K23" s="96" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="96" t="n"/>
+      <c r="B24" s="96" t="n"/>
+      <c r="C24" s="96" t="n"/>
+      <c r="D24" s="96" t="n"/>
+      <c r="E24" s="96" t="n"/>
+      <c r="F24" s="96" t="n"/>
+      <c r="G24" s="96" t="n"/>
+      <c r="H24" s="96" t="n"/>
+      <c r="I24" s="96" t="n"/>
+      <c r="J24" s="96" t="n"/>
+      <c r="K24" s="96" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="96" t="n"/>
+      <c r="B25" s="96" t="n"/>
+      <c r="C25" s="96" t="n"/>
+      <c r="D25" s="96" t="n"/>
+      <c r="E25" s="96" t="n"/>
+      <c r="F25" s="96" t="n"/>
+      <c r="G25" s="96" t="n"/>
+      <c r="H25" s="96" t="n"/>
+      <c r="I25" s="96" t="n"/>
+      <c r="J25" s="96" t="n"/>
+      <c r="K25" s="96" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="96" t="n"/>
+      <c r="B26" s="96" t="n"/>
+      <c r="C26" s="96" t="n"/>
+      <c r="D26" s="96" t="n"/>
+      <c r="E26" s="96" t="n"/>
+      <c r="F26" s="96" t="n"/>
+      <c r="G26" s="96" t="n"/>
+      <c r="H26" s="96" t="n"/>
+      <c r="I26" s="96" t="n"/>
+      <c r="J26" s="96" t="n"/>
+      <c r="K26" s="96" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="96" t="n"/>
+      <c r="B27" s="96" t="n"/>
+      <c r="C27" s="96" t="n"/>
+      <c r="D27" s="96" t="n"/>
+      <c r="E27" s="96" t="n"/>
+      <c r="F27" s="96" t="n"/>
+      <c r="G27" s="96" t="n"/>
+      <c r="H27" s="96" t="n"/>
+      <c r="I27" s="96" t="n"/>
+      <c r="J27" s="96" t="n"/>
+      <c r="K27" s="96" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="96" t="n"/>
+      <c r="B28" s="96" t="n"/>
+      <c r="C28" s="96" t="n"/>
+      <c r="D28" s="96" t="n"/>
+      <c r="E28" s="96" t="n"/>
+      <c r="F28" s="96" t="n"/>
+      <c r="G28" s="96" t="n"/>
+      <c r="H28" s="96" t="n"/>
+      <c r="I28" s="96" t="n"/>
+      <c r="J28" s="96" t="n"/>
+      <c r="K28" s="96" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="96" t="n"/>
+      <c r="B29" s="96" t="n"/>
+      <c r="C29" s="96" t="n"/>
+      <c r="D29" s="96" t="n"/>
+      <c r="E29" s="96" t="n"/>
+      <c r="F29" s="96" t="n"/>
+      <c r="G29" s="96" t="n"/>
+      <c r="H29" s="96" t="n"/>
+      <c r="I29" s="96" t="n"/>
+      <c r="J29" s="96" t="n"/>
+      <c r="K29" s="96" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="96" t="n"/>
+      <c r="B30" s="96" t="n"/>
+      <c r="C30" s="96" t="n"/>
+      <c r="D30" s="96" t="n"/>
+      <c r="E30" s="96" t="n"/>
+      <c r="F30" s="96" t="n"/>
+      <c r="G30" s="96" t="n"/>
+      <c r="H30" s="96" t="n"/>
+      <c r="I30" s="96" t="n"/>
+      <c r="J30" s="96" t="n"/>
+      <c r="K30" s="96" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="96" t="n"/>
+      <c r="B31" s="96" t="n"/>
+      <c r="C31" s="96" t="n"/>
+      <c r="D31" s="96" t="n"/>
+      <c r="E31" s="96" t="n"/>
+      <c r="F31" s="96" t="n"/>
+      <c r="G31" s="96" t="n"/>
+      <c r="H31" s="96" t="n"/>
+      <c r="I31" s="96" t="n"/>
+      <c r="J31" s="96" t="n"/>
+      <c r="K31" s="96" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="96" t="n"/>
+      <c r="B32" s="96" t="n"/>
+      <c r="C32" s="96" t="n"/>
+      <c r="D32" s="96" t="n"/>
+      <c r="E32" s="96" t="n"/>
+      <c r="F32" s="96" t="n"/>
+      <c r="G32" s="96" t="n"/>
+      <c r="H32" s="96" t="n"/>
+      <c r="I32" s="96" t="n"/>
+      <c r="J32" s="96" t="n"/>
+      <c r="K32" s="96" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="96" t="n"/>
+      <c r="B33" s="96" t="n"/>
+      <c r="C33" s="96" t="n"/>
+      <c r="D33" s="96" t="n"/>
+      <c r="E33" s="96" t="n"/>
+      <c r="F33" s="96" t="n"/>
+      <c r="G33" s="96" t="n"/>
+      <c r="H33" s="96" t="n"/>
+      <c r="I33" s="96" t="n"/>
+      <c r="J33" s="96" t="n"/>
+      <c r="K33" s="96" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="96" t="n"/>
+      <c r="B34" s="96" t="n"/>
+      <c r="C34" s="96" t="n"/>
+      <c r="D34" s="96" t="n"/>
+      <c r="E34" s="96" t="n"/>
+      <c r="F34" s="96" t="n"/>
+      <c r="G34" s="96" t="n"/>
+      <c r="H34" s="96" t="n"/>
+      <c r="I34" s="96" t="n"/>
+      <c r="J34" s="96" t="n"/>
+      <c r="K34" s="96" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="96" t="n"/>
+      <c r="B35" s="96" t="n"/>
+      <c r="C35" s="96" t="n"/>
+      <c r="D35" s="96" t="n"/>
+      <c r="E35" s="96" t="n"/>
+      <c r="F35" s="96" t="n"/>
+      <c r="G35" s="96" t="n"/>
+      <c r="H35" s="96" t="n"/>
+      <c r="I35" s="96" t="n"/>
+      <c r="J35" s="96" t="n"/>
+      <c r="K35" s="96" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="96" t="n"/>
+      <c r="B36" s="96" t="n"/>
+      <c r="C36" s="96" t="n"/>
+      <c r="D36" s="96" t="n"/>
+      <c r="E36" s="96" t="n"/>
+      <c r="F36" s="96" t="n"/>
+      <c r="G36" s="96" t="n"/>
+      <c r="H36" s="96" t="n"/>
+      <c r="I36" s="96" t="n"/>
+      <c r="J36" s="96" t="n"/>
+      <c r="K36" s="96" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="96" t="n"/>
+      <c r="B37" s="96" t="n"/>
+      <c r="C37" s="96" t="n"/>
+      <c r="D37" s="96" t="n"/>
+      <c r="E37" s="96" t="n"/>
+      <c r="F37" s="96" t="n"/>
+      <c r="G37" s="96" t="n"/>
+      <c r="H37" s="96" t="n"/>
+      <c r="I37" s="96" t="n"/>
+      <c r="J37" s="96" t="n"/>
+      <c r="K37" s="96" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="96" t="n"/>
+      <c r="B38" s="96" t="n"/>
+      <c r="C38" s="96" t="n"/>
+      <c r="D38" s="96" t="n"/>
+      <c r="E38" s="96" t="n"/>
+      <c r="F38" s="96" t="n"/>
+      <c r="G38" s="96" t="n"/>
+      <c r="H38" s="96" t="n"/>
+      <c r="I38" s="96" t="n"/>
+      <c r="J38" s="96" t="n"/>
+      <c r="K38" s="96" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="96" t="n"/>
+      <c r="B39" s="96" t="n"/>
+      <c r="C39" s="96" t="n"/>
+      <c r="D39" s="96" t="n"/>
+      <c r="E39" s="96" t="n"/>
+      <c r="F39" s="96" t="n"/>
+      <c r="G39" s="96" t="n"/>
+      <c r="H39" s="96" t="n"/>
+      <c r="I39" s="96" t="n"/>
+      <c r="J39" s="96" t="n"/>
+      <c r="K39" s="96" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="96" t="n"/>
+      <c r="B40" s="96" t="n"/>
+      <c r="C40" s="96" t="n"/>
+      <c r="D40" s="96" t="n"/>
+      <c r="E40" s="96" t="n"/>
+      <c r="F40" s="96" t="n"/>
+      <c r="G40" s="96" t="n"/>
+      <c r="H40" s="96" t="n"/>
+      <c r="I40" s="96" t="n"/>
+      <c r="J40" s="96" t="n"/>
+      <c r="K40" s="96" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="96" t="n"/>
+      <c r="B41" s="96" t="n"/>
+      <c r="C41" s="96" t="n"/>
+      <c r="D41" s="96" t="n"/>
+      <c r="E41" s="96" t="n"/>
+      <c r="F41" s="96" t="n"/>
+      <c r="G41" s="96" t="n"/>
+      <c r="H41" s="96" t="n"/>
+      <c r="I41" s="96" t="n"/>
+      <c r="J41" s="96" t="n"/>
+      <c r="K41" s="96" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="96" t="n"/>
+      <c r="B42" s="96" t="n"/>
+      <c r="C42" s="96" t="n"/>
+      <c r="D42" s="96" t="n"/>
+      <c r="E42" s="96" t="n"/>
+      <c r="F42" s="96" t="n"/>
+      <c r="G42" s="96" t="n"/>
+      <c r="H42" s="96" t="n"/>
+      <c r="I42" s="96" t="n"/>
+      <c r="J42" s="96" t="n"/>
+      <c r="K42" s="96" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="96" t="n"/>
+      <c r="B43" s="96" t="n"/>
+      <c r="C43" s="96" t="n"/>
+      <c r="D43" s="96" t="n"/>
+      <c r="E43" s="96" t="n"/>
+      <c r="F43" s="96" t="n"/>
+      <c r="G43" s="96" t="n"/>
+      <c r="H43" s="96" t="n"/>
+      <c r="I43" s="96" t="n"/>
+      <c r="J43" s="96" t="n"/>
+      <c r="K43" s="96" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="96" t="n"/>
+      <c r="B44" s="96" t="n"/>
+      <c r="C44" s="96" t="n"/>
+      <c r="D44" s="96" t="n"/>
+      <c r="E44" s="96" t="n"/>
+      <c r="F44" s="96" t="n"/>
+      <c r="G44" s="96" t="n"/>
+      <c r="H44" s="96" t="n"/>
+      <c r="I44" s="96" t="n"/>
+      <c r="J44" s="96" t="n"/>
+      <c r="K44" s="96" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="96" t="n"/>
+      <c r="B45" s="96" t="n"/>
+      <c r="C45" s="96" t="n"/>
+      <c r="D45" s="96" t="n"/>
+      <c r="E45" s="96" t="n"/>
+      <c r="F45" s="96" t="n"/>
+      <c r="G45" s="96" t="n"/>
+      <c r="H45" s="96" t="n"/>
+      <c r="I45" s="96" t="n"/>
+      <c r="J45" s="96" t="n"/>
+      <c r="K45" s="96" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="96" t="n"/>
+      <c r="B46" s="96" t="n"/>
+      <c r="C46" s="96" t="n"/>
+      <c r="D46" s="96" t="n"/>
+      <c r="E46" s="96" t="n"/>
+      <c r="F46" s="96" t="n"/>
+      <c r="G46" s="96" t="n"/>
+      <c r="H46" s="96" t="n"/>
+      <c r="I46" s="96" t="n"/>
+      <c r="J46" s="96" t="n"/>
+      <c r="K46" s="96" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="96" t="n"/>
+      <c r="B47" s="96" t="n"/>
+      <c r="C47" s="96" t="n"/>
+      <c r="D47" s="96" t="n"/>
+      <c r="E47" s="96" t="n"/>
+      <c r="F47" s="96" t="n"/>
+      <c r="G47" s="96" t="n"/>
+      <c r="H47" s="96" t="n"/>
+      <c r="I47" s="96" t="n"/>
+      <c r="J47" s="96" t="n"/>
+      <c r="K47" s="96" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="96" t="n"/>
+      <c r="B48" s="96" t="n"/>
+      <c r="C48" s="96" t="n"/>
+      <c r="D48" s="96" t="n"/>
+      <c r="E48" s="96" t="n"/>
+      <c r="F48" s="96" t="n"/>
+      <c r="G48" s="96" t="n"/>
+      <c r="H48" s="96" t="n"/>
+      <c r="I48" s="96" t="n"/>
+      <c r="J48" s="96" t="n"/>
+      <c r="K48" s="96" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="101" t="inlineStr">
+        <is>
+          <t>LOOKUP TABLE (DO NOT EDIT)</t>
+        </is>
+      </c>
+      <c r="B49" s="96" t="n"/>
+      <c r="C49" s="96" t="n"/>
+      <c r="D49" s="96" t="n"/>
+      <c r="E49" s="96" t="n"/>
+      <c r="F49" s="96" t="n"/>
+      <c r="G49" s="96" t="n"/>
+      <c r="H49" s="96" t="n"/>
+      <c r="I49" s="96" t="n"/>
+      <c r="J49" s="96" t="n"/>
+      <c r="K49" s="96" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="102" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B50" s="102" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C50" s="102" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D50" s="102" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E50" s="102" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F50" s="102" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G50" s="102" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H50" s="102" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I50" s="102" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J50" s="102" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K50" s="102" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L50" s="103" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M50" s="103" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="102" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B51" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!B8,IF($B$6="Affirm",'Product Line Summary'!B16,IF($B$6="InsureSight",'Product Line Summary'!B24,'Product Line Summary'!B32)))</f>
+        <v/>
+      </c>
+      <c r="C51" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!C8,IF($B$6="Affirm",'Product Line Summary'!C16,IF($B$6="InsureSight",'Product Line Summary'!C24,'Product Line Summary'!C32)))</f>
+        <v/>
+      </c>
+      <c r="D51" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!D8,IF($B$6="Affirm",'Product Line Summary'!D16,IF($B$6="InsureSight",'Product Line Summary'!D24,'Product Line Summary'!D32)))</f>
+        <v/>
+      </c>
+      <c r="E51" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!E8,IF($B$6="Affirm",'Product Line Summary'!E16,IF($B$6="InsureSight",'Product Line Summary'!E24,'Product Line Summary'!E32)))</f>
+        <v/>
+      </c>
+      <c r="F51" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!F8,IF($B$6="Affirm",'Product Line Summary'!F16,IF($B$6="InsureSight",'Product Line Summary'!F24,'Product Line Summary'!F32)))</f>
+        <v/>
+      </c>
+      <c r="G51" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!G8,IF($B$6="Affirm",'Product Line Summary'!G16,IF($B$6="InsureSight",'Product Line Summary'!G24,'Product Line Summary'!G32)))</f>
+        <v/>
+      </c>
+      <c r="H51" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!H8,IF($B$6="Affirm",'Product Line Summary'!H16,IF($B$6="InsureSight",'Product Line Summary'!H24,'Product Line Summary'!H32)))</f>
+        <v/>
+      </c>
+      <c r="I51" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!I8,IF($B$6="Affirm",'Product Line Summary'!I16,IF($B$6="InsureSight",'Product Line Summary'!I24,'Product Line Summary'!I32)))</f>
+        <v/>
+      </c>
+      <c r="J51" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!J8,IF($B$6="Affirm",'Product Line Summary'!J16,IF($B$6="InsureSight",'Product Line Summary'!J24,'Product Line Summary'!J32)))</f>
+        <v/>
+      </c>
+      <c r="K51" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!K8,IF($B$6="Affirm",'Product Line Summary'!K16,IF($B$6="InsureSight",'Product Line Summary'!K24,'Product Line Summary'!K32)))</f>
+        <v/>
+      </c>
+      <c r="L51" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!L8,IF($B$6="Affirm",'Product Line Summary'!L16,IF($B$6="InsureSight",'Product Line Summary'!L24,'Product Line Summary'!L32)))</f>
+        <v/>
+      </c>
+      <c r="M51" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!M8,IF($B$6="Affirm",'Product Line Summary'!M16,IF($B$6="InsureSight",'Product Line Summary'!M24,'Product Line Summary'!M32)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="102" t="inlineStr">
+        <is>
+          <t>Cost of Revenue</t>
+        </is>
+      </c>
+      <c r="B52" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!B9,IF($B$6="Affirm",'Product Line Summary'!B17,IF($B$6="InsureSight",'Product Line Summary'!B25,'Product Line Summary'!B33)))</f>
+        <v/>
+      </c>
+      <c r="C52" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!C9,IF($B$6="Affirm",'Product Line Summary'!C17,IF($B$6="InsureSight",'Product Line Summary'!C25,'Product Line Summary'!C33)))</f>
+        <v/>
+      </c>
+      <c r="D52" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!D9,IF($B$6="Affirm",'Product Line Summary'!D17,IF($B$6="InsureSight",'Product Line Summary'!D25,'Product Line Summary'!D33)))</f>
+        <v/>
+      </c>
+      <c r="E52" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!E9,IF($B$6="Affirm",'Product Line Summary'!E17,IF($B$6="InsureSight",'Product Line Summary'!E25,'Product Line Summary'!E33)))</f>
+        <v/>
+      </c>
+      <c r="F52" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!F9,IF($B$6="Affirm",'Product Line Summary'!F17,IF($B$6="InsureSight",'Product Line Summary'!F25,'Product Line Summary'!F33)))</f>
+        <v/>
+      </c>
+      <c r="G52" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!G9,IF($B$6="Affirm",'Product Line Summary'!G17,IF($B$6="InsureSight",'Product Line Summary'!G25,'Product Line Summary'!G33)))</f>
+        <v/>
+      </c>
+      <c r="H52" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!H9,IF($B$6="Affirm",'Product Line Summary'!H17,IF($B$6="InsureSight",'Product Line Summary'!H25,'Product Line Summary'!H33)))</f>
+        <v/>
+      </c>
+      <c r="I52" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!I9,IF($B$6="Affirm",'Product Line Summary'!I17,IF($B$6="InsureSight",'Product Line Summary'!I25,'Product Line Summary'!I33)))</f>
+        <v/>
+      </c>
+      <c r="J52" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!J9,IF($B$6="Affirm",'Product Line Summary'!J17,IF($B$6="InsureSight",'Product Line Summary'!J25,'Product Line Summary'!J33)))</f>
+        <v/>
+      </c>
+      <c r="K52" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!K9,IF($B$6="Affirm",'Product Line Summary'!K17,IF($B$6="InsureSight",'Product Line Summary'!K25,'Product Line Summary'!K33)))</f>
+        <v/>
+      </c>
+      <c r="L52" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!L9,IF($B$6="Affirm",'Product Line Summary'!L17,IF($B$6="InsureSight",'Product Line Summary'!L25,'Product Line Summary'!L33)))</f>
+        <v/>
+      </c>
+      <c r="M52" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!M9,IF($B$6="Affirm",'Product Line Summary'!M17,IF($B$6="InsureSight",'Product Line Summary'!M25,'Product Line Summary'!M33)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="102" t="inlineStr">
+        <is>
+          <t>Contribution Margin $</t>
+        </is>
+      </c>
+      <c r="B53" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!B10,IF($B$6="Affirm",'Product Line Summary'!B18,IF($B$6="InsureSight",'Product Line Summary'!B26,'Product Line Summary'!B34)))</f>
+        <v/>
+      </c>
+      <c r="C53" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!C10,IF($B$6="Affirm",'Product Line Summary'!C18,IF($B$6="InsureSight",'Product Line Summary'!C26,'Product Line Summary'!C34)))</f>
+        <v/>
+      </c>
+      <c r="D53" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!D10,IF($B$6="Affirm",'Product Line Summary'!D18,IF($B$6="InsureSight",'Product Line Summary'!D26,'Product Line Summary'!D34)))</f>
+        <v/>
+      </c>
+      <c r="E53" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!E10,IF($B$6="Affirm",'Product Line Summary'!E18,IF($B$6="InsureSight",'Product Line Summary'!E26,'Product Line Summary'!E34)))</f>
+        <v/>
+      </c>
+      <c r="F53" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!F10,IF($B$6="Affirm",'Product Line Summary'!F18,IF($B$6="InsureSight",'Product Line Summary'!F26,'Product Line Summary'!F34)))</f>
+        <v/>
+      </c>
+      <c r="G53" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!G10,IF($B$6="Affirm",'Product Line Summary'!G18,IF($B$6="InsureSight",'Product Line Summary'!G26,'Product Line Summary'!G34)))</f>
+        <v/>
+      </c>
+      <c r="H53" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!H10,IF($B$6="Affirm",'Product Line Summary'!H18,IF($B$6="InsureSight",'Product Line Summary'!H26,'Product Line Summary'!H34)))</f>
+        <v/>
+      </c>
+      <c r="I53" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!I10,IF($B$6="Affirm",'Product Line Summary'!I18,IF($B$6="InsureSight",'Product Line Summary'!I26,'Product Line Summary'!I34)))</f>
+        <v/>
+      </c>
+      <c r="J53" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!J10,IF($B$6="Affirm",'Product Line Summary'!J18,IF($B$6="InsureSight",'Product Line Summary'!J26,'Product Line Summary'!J34)))</f>
+        <v/>
+      </c>
+      <c r="K53" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!K10,IF($B$6="Affirm",'Product Line Summary'!K18,IF($B$6="InsureSight",'Product Line Summary'!K26,'Product Line Summary'!K34)))</f>
+        <v/>
+      </c>
+      <c r="L53" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!L10,IF($B$6="Affirm",'Product Line Summary'!L18,IF($B$6="InsureSight",'Product Line Summary'!L26,'Product Line Summary'!L34)))</f>
+        <v/>
+      </c>
+      <c r="M53" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!M10,IF($B$6="Affirm",'Product Line Summary'!M18,IF($B$6="InsureSight",'Product Line Summary'!M26,'Product Line Summary'!M34)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="102" t="inlineStr">
+        <is>
+          <t>Contribution Margin %</t>
+        </is>
+      </c>
+      <c r="B54" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!B11,IF($B$6="Affirm",'Product Line Summary'!B19,IF($B$6="InsureSight",'Product Line Summary'!B27,'Product Line Summary'!B35)))</f>
+        <v/>
+      </c>
+      <c r="C54" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!C11,IF($B$6="Affirm",'Product Line Summary'!C19,IF($B$6="InsureSight",'Product Line Summary'!C27,'Product Line Summary'!C35)))</f>
+        <v/>
+      </c>
+      <c r="D54" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!D11,IF($B$6="Affirm",'Product Line Summary'!D19,IF($B$6="InsureSight",'Product Line Summary'!D27,'Product Line Summary'!D35)))</f>
+        <v/>
+      </c>
+      <c r="E54" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!E11,IF($B$6="Affirm",'Product Line Summary'!E19,IF($B$6="InsureSight",'Product Line Summary'!E27,'Product Line Summary'!E35)))</f>
+        <v/>
+      </c>
+      <c r="F54" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!F11,IF($B$6="Affirm",'Product Line Summary'!F19,IF($B$6="InsureSight",'Product Line Summary'!F27,'Product Line Summary'!F35)))</f>
+        <v/>
+      </c>
+      <c r="G54" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!G11,IF($B$6="Affirm",'Product Line Summary'!G19,IF($B$6="InsureSight",'Product Line Summary'!G27,'Product Line Summary'!G35)))</f>
+        <v/>
+      </c>
+      <c r="H54" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!H11,IF($B$6="Affirm",'Product Line Summary'!H19,IF($B$6="InsureSight",'Product Line Summary'!H27,'Product Line Summary'!H35)))</f>
+        <v/>
+      </c>
+      <c r="I54" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!I11,IF($B$6="Affirm",'Product Line Summary'!I19,IF($B$6="InsureSight",'Product Line Summary'!I27,'Product Line Summary'!I35)))</f>
+        <v/>
+      </c>
+      <c r="J54" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!J11,IF($B$6="Affirm",'Product Line Summary'!J19,IF($B$6="InsureSight",'Product Line Summary'!J27,'Product Line Summary'!J35)))</f>
+        <v/>
+      </c>
+      <c r="K54" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!K11,IF($B$6="Affirm",'Product Line Summary'!K19,IF($B$6="InsureSight",'Product Line Summary'!K27,'Product Line Summary'!K35)))</f>
+        <v/>
+      </c>
+      <c r="L54" s="13">
+        <f>IF($B$6="iGO",'Product Line Summary'!L11,IF($B$6="Affirm",'Product Line Summary'!L19,IF($B$6="InsureSight",'Product Line Summary'!L27,'Product Line Summary'!L35)))</f>
+        <v/>
+      </c>
+      <c r="M54" s="13">
+        <f>IF($B$6="iGO",'Product Line Summary'!M11,IF($B$6="Affirm",'Product Line Summary'!M19,IF($B$6="InsureSight",'Product Line Summary'!M27,'Product Line Summary'!M35)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="102" t="inlineStr">
+        <is>
+          <t>CM + R&amp;D $</t>
+        </is>
+      </c>
+      <c r="B55" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!B12,IF($B$6="Affirm",'Product Line Summary'!B20,IF($B$6="InsureSight",'Product Line Summary'!B28,'Product Line Summary'!B36)))</f>
+        <v/>
+      </c>
+      <c r="C55" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!C12,IF($B$6="Affirm",'Product Line Summary'!C20,IF($B$6="InsureSight",'Product Line Summary'!C28,'Product Line Summary'!C36)))</f>
+        <v/>
+      </c>
+      <c r="D55" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!D12,IF($B$6="Affirm",'Product Line Summary'!D20,IF($B$6="InsureSight",'Product Line Summary'!D28,'Product Line Summary'!D36)))</f>
+        <v/>
+      </c>
+      <c r="E55" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!E12,IF($B$6="Affirm",'Product Line Summary'!E20,IF($B$6="InsureSight",'Product Line Summary'!E28,'Product Line Summary'!E36)))</f>
+        <v/>
+      </c>
+      <c r="F55" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!F12,IF($B$6="Affirm",'Product Line Summary'!F20,IF($B$6="InsureSight",'Product Line Summary'!F28,'Product Line Summary'!F36)))</f>
+        <v/>
+      </c>
+      <c r="G55" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!G12,IF($B$6="Affirm",'Product Line Summary'!G20,IF($B$6="InsureSight",'Product Line Summary'!G28,'Product Line Summary'!G36)))</f>
+        <v/>
+      </c>
+      <c r="H55" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!H12,IF($B$6="Affirm",'Product Line Summary'!H20,IF($B$6="InsureSight",'Product Line Summary'!H28,'Product Line Summary'!H36)))</f>
+        <v/>
+      </c>
+      <c r="I55" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!I12,IF($B$6="Affirm",'Product Line Summary'!I20,IF($B$6="InsureSight",'Product Line Summary'!I28,'Product Line Summary'!I36)))</f>
+        <v/>
+      </c>
+      <c r="J55" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!J12,IF($B$6="Affirm",'Product Line Summary'!J20,IF($B$6="InsureSight",'Product Line Summary'!J28,'Product Line Summary'!J36)))</f>
+        <v/>
+      </c>
+      <c r="K55" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!K12,IF($B$6="Affirm",'Product Line Summary'!K20,IF($B$6="InsureSight",'Product Line Summary'!K28,'Product Line Summary'!K36)))</f>
+        <v/>
+      </c>
+      <c r="L55" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!L12,IF($B$6="Affirm",'Product Line Summary'!L20,IF($B$6="InsureSight",'Product Line Summary'!L28,'Product Line Summary'!L36)))</f>
+        <v/>
+      </c>
+      <c r="M55" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!M12,IF($B$6="Affirm",'Product Line Summary'!M20,IF($B$6="InsureSight",'Product Line Summary'!M28,'Product Line Summary'!M36)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="102" t="inlineStr">
+        <is>
+          <t>CM + R&amp;D %</t>
+        </is>
+      </c>
+      <c r="B56" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!B13,IF($B$6="Affirm",'Product Line Summary'!B21,IF($B$6="InsureSight",'Product Line Summary'!B29,'Product Line Summary'!B37)))</f>
+        <v/>
+      </c>
+      <c r="C56" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!C13,IF($B$6="Affirm",'Product Line Summary'!C21,IF($B$6="InsureSight",'Product Line Summary'!C29,'Product Line Summary'!C37)))</f>
+        <v/>
+      </c>
+      <c r="D56" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!D13,IF($B$6="Affirm",'Product Line Summary'!D21,IF($B$6="InsureSight",'Product Line Summary'!D29,'Product Line Summary'!D37)))</f>
+        <v/>
+      </c>
+      <c r="E56" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!E13,IF($B$6="Affirm",'Product Line Summary'!E21,IF($B$6="InsureSight",'Product Line Summary'!E29,'Product Line Summary'!E37)))</f>
+        <v/>
+      </c>
+      <c r="F56" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!F13,IF($B$6="Affirm",'Product Line Summary'!F21,IF($B$6="InsureSight",'Product Line Summary'!F29,'Product Line Summary'!F37)))</f>
+        <v/>
+      </c>
+      <c r="G56" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!G13,IF($B$6="Affirm",'Product Line Summary'!G21,IF($B$6="InsureSight",'Product Line Summary'!G29,'Product Line Summary'!G37)))</f>
+        <v/>
+      </c>
+      <c r="H56" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!H13,IF($B$6="Affirm",'Product Line Summary'!H21,IF($B$6="InsureSight",'Product Line Summary'!H29,'Product Line Summary'!H37)))</f>
+        <v/>
+      </c>
+      <c r="I56" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!I13,IF($B$6="Affirm",'Product Line Summary'!I21,IF($B$6="InsureSight",'Product Line Summary'!I29,'Product Line Summary'!I37)))</f>
+        <v/>
+      </c>
+      <c r="J56" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!J13,IF($B$6="Affirm",'Product Line Summary'!J21,IF($B$6="InsureSight",'Product Line Summary'!J29,'Product Line Summary'!J37)))</f>
+        <v/>
+      </c>
+      <c r="K56" s="106">
+        <f>IF($B$6="iGO",'Product Line Summary'!K13,IF($B$6="Affirm",'Product Line Summary'!K21,IF($B$6="InsureSight",'Product Line Summary'!K29,'Product Line Summary'!K37)))</f>
+        <v/>
+      </c>
+      <c r="L56" s="13">
+        <f>IF($B$6="iGO",'Product Line Summary'!L13,IF($B$6="Affirm",'Product Line Summary'!L21,IF($B$6="InsureSight",'Product Line Summary'!L29,'Product Line Summary'!L37)))</f>
+        <v/>
+      </c>
+      <c r="M56" s="13">
+        <f>IF($B$6="iGO",'Product Line Summary'!M13,IF($B$6="Affirm",'Product Line Summary'!M21,IF($B$6="InsureSight",'Product Line Summary'!M29,'Product Line Summary'!M37)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="96" t="n"/>
+      <c r="B57" s="96" t="n"/>
+      <c r="C57" s="96" t="n"/>
+      <c r="D57" s="96" t="n"/>
+      <c r="E57" s="96" t="n"/>
+      <c r="F57" s="96" t="n"/>
+      <c r="G57" s="96" t="n"/>
+      <c r="H57" s="96" t="n"/>
+      <c r="I57" s="96" t="n"/>
+      <c r="J57" s="96" t="n"/>
+      <c r="K57" s="96" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="102" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B58" s="102" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C58" s="102" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D58" s="102" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E58" s="102" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F58" s="102" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G58" s="102" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H58" s="102" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I58" s="102" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J58" s="102" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K58" s="102" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L58" s="103" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M58" s="103" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="102" t="inlineStr">
+        <is>
+          <t>NetOps</t>
+        </is>
+      </c>
+      <c r="B59" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!B43,IF($B$6="Affirm",'Product Line Summary'!B53,IF($B$6="InsureSight",'Product Line Summary'!B63,'Product Line Summary'!B73)))</f>
+        <v/>
+      </c>
+      <c r="C59" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!C43,IF($B$6="Affirm",'Product Line Summary'!C53,IF($B$6="InsureSight",'Product Line Summary'!C63,'Product Line Summary'!C73)))</f>
+        <v/>
+      </c>
+      <c r="D59" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!D43,IF($B$6="Affirm",'Product Line Summary'!D53,IF($B$6="InsureSight",'Product Line Summary'!D63,'Product Line Summary'!D73)))</f>
+        <v/>
+      </c>
+      <c r="E59" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!E43,IF($B$6="Affirm",'Product Line Summary'!E53,IF($B$6="InsureSight",'Product Line Summary'!E63,'Product Line Summary'!E73)))</f>
+        <v/>
+      </c>
+      <c r="F59" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!F43,IF($B$6="Affirm",'Product Line Summary'!F53,IF($B$6="InsureSight",'Product Line Summary'!F63,'Product Line Summary'!F73)))</f>
+        <v/>
+      </c>
+      <c r="G59" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!G43,IF($B$6="Affirm",'Product Line Summary'!G53,IF($B$6="InsureSight",'Product Line Summary'!G63,'Product Line Summary'!G73)))</f>
+        <v/>
+      </c>
+      <c r="H59" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!H43,IF($B$6="Affirm",'Product Line Summary'!H53,IF($B$6="InsureSight",'Product Line Summary'!H63,'Product Line Summary'!H73)))</f>
+        <v/>
+      </c>
+      <c r="I59" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!I43,IF($B$6="Affirm",'Product Line Summary'!I53,IF($B$6="InsureSight",'Product Line Summary'!I63,'Product Line Summary'!I73)))</f>
+        <v/>
+      </c>
+      <c r="J59" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!J43,IF($B$6="Affirm",'Product Line Summary'!J53,IF($B$6="InsureSight",'Product Line Summary'!J63,'Product Line Summary'!J73)))</f>
+        <v/>
+      </c>
+      <c r="K59" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!K43,IF($B$6="Affirm",'Product Line Summary'!K53,IF($B$6="InsureSight",'Product Line Summary'!K63,'Product Line Summary'!K73)))</f>
+        <v/>
+      </c>
+      <c r="L59" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!L43,IF($B$6="Affirm",'Product Line Summary'!L53,IF($B$6="InsureSight",'Product Line Summary'!L63,'Product Line Summary'!L73)))</f>
+        <v/>
+      </c>
+      <c r="M59" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!M43,IF($B$6="Affirm",'Product Line Summary'!M53,IF($B$6="InsureSight",'Product Line Summary'!M63,'Product Line Summary'!M73)))</f>
+        <v/>
+      </c>
+      <c r="N59" s="105">
+        <f>SUM(B59:M59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="102" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B60" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!B44,IF($B$6="Affirm",'Product Line Summary'!B54,IF($B$6="InsureSight",'Product Line Summary'!B64,'Product Line Summary'!B74)))</f>
+        <v/>
+      </c>
+      <c r="C60" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!C44,IF($B$6="Affirm",'Product Line Summary'!C54,IF($B$6="InsureSight",'Product Line Summary'!C64,'Product Line Summary'!C74)))</f>
+        <v/>
+      </c>
+      <c r="D60" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!D44,IF($B$6="Affirm",'Product Line Summary'!D54,IF($B$6="InsureSight",'Product Line Summary'!D64,'Product Line Summary'!D74)))</f>
+        <v/>
+      </c>
+      <c r="E60" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!E44,IF($B$6="Affirm",'Product Line Summary'!E54,IF($B$6="InsureSight",'Product Line Summary'!E64,'Product Line Summary'!E74)))</f>
+        <v/>
+      </c>
+      <c r="F60" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!F44,IF($B$6="Affirm",'Product Line Summary'!F54,IF($B$6="InsureSight",'Product Line Summary'!F64,'Product Line Summary'!F74)))</f>
+        <v/>
+      </c>
+      <c r="G60" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!G44,IF($B$6="Affirm",'Product Line Summary'!G54,IF($B$6="InsureSight",'Product Line Summary'!G64,'Product Line Summary'!G74)))</f>
+        <v/>
+      </c>
+      <c r="H60" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!H44,IF($B$6="Affirm",'Product Line Summary'!H54,IF($B$6="InsureSight",'Product Line Summary'!H64,'Product Line Summary'!H74)))</f>
+        <v/>
+      </c>
+      <c r="I60" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!I44,IF($B$6="Affirm",'Product Line Summary'!I54,IF($B$6="InsureSight",'Product Line Summary'!I64,'Product Line Summary'!I74)))</f>
+        <v/>
+      </c>
+      <c r="J60" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!J44,IF($B$6="Affirm",'Product Line Summary'!J54,IF($B$6="InsureSight",'Product Line Summary'!J64,'Product Line Summary'!J74)))</f>
+        <v/>
+      </c>
+      <c r="K60" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!K44,IF($B$6="Affirm",'Product Line Summary'!K54,IF($B$6="InsureSight",'Product Line Summary'!K64,'Product Line Summary'!K74)))</f>
+        <v/>
+      </c>
+      <c r="L60" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!L44,IF($B$6="Affirm",'Product Line Summary'!L54,IF($B$6="InsureSight",'Product Line Summary'!L64,'Product Line Summary'!L74)))</f>
+        <v/>
+      </c>
+      <c r="M60" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!M44,IF($B$6="Affirm",'Product Line Summary'!M54,IF($B$6="InsureSight",'Product Line Summary'!M64,'Product Line Summary'!M74)))</f>
+        <v/>
+      </c>
+      <c r="N60" s="105">
+        <f>SUM(B60:M60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="102" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="B61" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!B45,IF($B$6="Affirm",'Product Line Summary'!B55,IF($B$6="InsureSight",'Product Line Summary'!B65,'Product Line Summary'!B75)))</f>
+        <v/>
+      </c>
+      <c r="C61" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!C45,IF($B$6="Affirm",'Product Line Summary'!C55,IF($B$6="InsureSight",'Product Line Summary'!C65,'Product Line Summary'!C75)))</f>
+        <v/>
+      </c>
+      <c r="D61" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!D45,IF($B$6="Affirm",'Product Line Summary'!D55,IF($B$6="InsureSight",'Product Line Summary'!D65,'Product Line Summary'!D75)))</f>
+        <v/>
+      </c>
+      <c r="E61" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!E45,IF($B$6="Affirm",'Product Line Summary'!E55,IF($B$6="InsureSight",'Product Line Summary'!E65,'Product Line Summary'!E75)))</f>
+        <v/>
+      </c>
+      <c r="F61" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!F45,IF($B$6="Affirm",'Product Line Summary'!F55,IF($B$6="InsureSight",'Product Line Summary'!F65,'Product Line Summary'!F75)))</f>
+        <v/>
+      </c>
+      <c r="G61" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!G45,IF($B$6="Affirm",'Product Line Summary'!G55,IF($B$6="InsureSight",'Product Line Summary'!G65,'Product Line Summary'!G75)))</f>
+        <v/>
+      </c>
+      <c r="H61" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!H45,IF($B$6="Affirm",'Product Line Summary'!H55,IF($B$6="InsureSight",'Product Line Summary'!H65,'Product Line Summary'!H75)))</f>
+        <v/>
+      </c>
+      <c r="I61" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!I45,IF($B$6="Affirm",'Product Line Summary'!I55,IF($B$6="InsureSight",'Product Line Summary'!I65,'Product Line Summary'!I75)))</f>
+        <v/>
+      </c>
+      <c r="J61" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!J45,IF($B$6="Affirm",'Product Line Summary'!J55,IF($B$6="InsureSight",'Product Line Summary'!J65,'Product Line Summary'!J75)))</f>
+        <v/>
+      </c>
+      <c r="K61" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!K45,IF($B$6="Affirm",'Product Line Summary'!K55,IF($B$6="InsureSight",'Product Line Summary'!K65,'Product Line Summary'!K75)))</f>
+        <v/>
+      </c>
+      <c r="L61" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!L45,IF($B$6="Affirm",'Product Line Summary'!L55,IF($B$6="InsureSight",'Product Line Summary'!L65,'Product Line Summary'!L75)))</f>
+        <v/>
+      </c>
+      <c r="M61" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!M45,IF($B$6="Affirm",'Product Line Summary'!M55,IF($B$6="InsureSight",'Product Line Summary'!M65,'Product Line Summary'!M75)))</f>
+        <v/>
+      </c>
+      <c r="N61" s="105">
+        <f>SUM(B61:M61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="100" t="inlineStr">
+        <is>
+          <t>SECTION 2: ALL-PRODUCTS COMPARISON</t>
+        </is>
+      </c>
+      <c r="B62" s="107">
+        <f>IF($B$6="iGO",'Product Line Summary'!B46,IF($B$6="Affirm",'Product Line Summary'!B56,IF($B$6="InsureSight",'Product Line Summary'!B66,'Product Line Summary'!B76)))</f>
+        <v/>
+      </c>
+      <c r="C62" s="107">
+        <f>IF($B$6="iGO",'Product Line Summary'!C46,IF($B$6="Affirm",'Product Line Summary'!C56,IF($B$6="InsureSight",'Product Line Summary'!C66,'Product Line Summary'!C76)))</f>
+        <v/>
+      </c>
+      <c r="D62" s="107">
+        <f>IF($B$6="iGO",'Product Line Summary'!D46,IF($B$6="Affirm",'Product Line Summary'!D56,IF($B$6="InsureSight",'Product Line Summary'!D66,'Product Line Summary'!D76)))</f>
+        <v/>
+      </c>
+      <c r="E62" s="107">
+        <f>IF($B$6="iGO",'Product Line Summary'!E46,IF($B$6="Affirm",'Product Line Summary'!E56,IF($B$6="InsureSight",'Product Line Summary'!E66,'Product Line Summary'!E76)))</f>
+        <v/>
+      </c>
+      <c r="F62" s="107">
+        <f>IF($B$6="iGO",'Product Line Summary'!F46,IF($B$6="Affirm",'Product Line Summary'!F56,IF($B$6="InsureSight",'Product Line Summary'!F66,'Product Line Summary'!F76)))</f>
+        <v/>
+      </c>
+      <c r="G62" s="107">
+        <f>IF($B$6="iGO",'Product Line Summary'!G46,IF($B$6="Affirm",'Product Line Summary'!G56,IF($B$6="InsureSight",'Product Line Summary'!G66,'Product Line Summary'!G76)))</f>
+        <v/>
+      </c>
+      <c r="H62" s="107">
+        <f>IF($B$6="iGO",'Product Line Summary'!H46,IF($B$6="Affirm",'Product Line Summary'!H56,IF($B$6="InsureSight",'Product Line Summary'!H66,'Product Line Summary'!H76)))</f>
+        <v/>
+      </c>
+      <c r="I62" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!I46,IF($B$6="Affirm",'Product Line Summary'!I56,IF($B$6="InsureSight",'Product Line Summary'!I66,'Product Line Summary'!I76)))</f>
+        <v/>
+      </c>
+      <c r="J62" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!J46,IF($B$6="Affirm",'Product Line Summary'!J56,IF($B$6="InsureSight",'Product Line Summary'!J66,'Product Line Summary'!J76)))</f>
+        <v/>
+      </c>
+      <c r="K62" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!K46,IF($B$6="Affirm",'Product Line Summary'!K56,IF($B$6="InsureSight",'Product Line Summary'!K66,'Product Line Summary'!K76)))</f>
+        <v/>
+      </c>
+      <c r="L62" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!L46,IF($B$6="Affirm",'Product Line Summary'!L56,IF($B$6="InsureSight",'Product Line Summary'!L66,'Product Line Summary'!L76)))</f>
+        <v/>
+      </c>
+      <c r="M62" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!M46,IF($B$6="Affirm",'Product Line Summary'!M56,IF($B$6="InsureSight",'Product Line Summary'!M66,'Product Line Summary'!M76)))</f>
+        <v/>
+      </c>
+      <c r="N62" s="105">
+        <f>SUM(B62:M62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="102" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B63" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!B47,IF($B$6="Affirm",'Product Line Summary'!B57,IF($B$6="InsureSight",'Product Line Summary'!B67,'Product Line Summary'!B77)))</f>
+        <v/>
+      </c>
+      <c r="C63" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!C47,IF($B$6="Affirm",'Product Line Summary'!C57,IF($B$6="InsureSight",'Product Line Summary'!C67,'Product Line Summary'!C77)))</f>
+        <v/>
+      </c>
+      <c r="D63" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!D47,IF($B$6="Affirm",'Product Line Summary'!D57,IF($B$6="InsureSight",'Product Line Summary'!D67,'Product Line Summary'!D77)))</f>
+        <v/>
+      </c>
+      <c r="E63" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!E47,IF($B$6="Affirm",'Product Line Summary'!E57,IF($B$6="InsureSight",'Product Line Summary'!E67,'Product Line Summary'!E77)))</f>
+        <v/>
+      </c>
+      <c r="F63" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!F47,IF($B$6="Affirm",'Product Line Summary'!F57,IF($B$6="InsureSight",'Product Line Summary'!F67,'Product Line Summary'!F77)))</f>
+        <v/>
+      </c>
+      <c r="G63" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!G47,IF($B$6="Affirm",'Product Line Summary'!G57,IF($B$6="InsureSight",'Product Line Summary'!G67,'Product Line Summary'!G77)))</f>
+        <v/>
+      </c>
+      <c r="H63" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!H47,IF($B$6="Affirm",'Product Line Summary'!H57,IF($B$6="InsureSight",'Product Line Summary'!H67,'Product Line Summary'!H77)))</f>
+        <v/>
+      </c>
+      <c r="I63" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!I47,IF($B$6="Affirm",'Product Line Summary'!I57,IF($B$6="InsureSight",'Product Line Summary'!I67,'Product Line Summary'!I77)))</f>
+        <v/>
+      </c>
+      <c r="J63" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!J47,IF($B$6="Affirm",'Product Line Summary'!J57,IF($B$6="InsureSight",'Product Line Summary'!J67,'Product Line Summary'!J77)))</f>
+        <v/>
+      </c>
+      <c r="K63" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!K47,IF($B$6="Affirm",'Product Line Summary'!K57,IF($B$6="InsureSight",'Product Line Summary'!K67,'Product Line Summary'!K77)))</f>
+        <v/>
+      </c>
+      <c r="L63" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!L47,IF($B$6="Affirm",'Product Line Summary'!L57,IF($B$6="InsureSight",'Product Line Summary'!L67,'Product Line Summary'!L77)))</f>
+        <v/>
+      </c>
+      <c r="M63" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!M47,IF($B$6="Affirm",'Product Line Summary'!M57,IF($B$6="InsureSight",'Product Line Summary'!M67,'Product Line Summary'!M77)))</f>
+        <v/>
+      </c>
+      <c r="N63" s="105">
+        <f>SUM(B63:M63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="102" t="inlineStr">
+        <is>
+          <t>Research &amp; Development</t>
+        </is>
+      </c>
+      <c r="B64" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!B48,IF($B$6="Affirm",'Product Line Summary'!B58,IF($B$6="InsureSight",'Product Line Summary'!B68,'Product Line Summary'!B78)))</f>
+        <v/>
+      </c>
+      <c r="C64" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!C48,IF($B$6="Affirm",'Product Line Summary'!C58,IF($B$6="InsureSight",'Product Line Summary'!C68,'Product Line Summary'!C78)))</f>
+        <v/>
+      </c>
+      <c r="D64" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!D48,IF($B$6="Affirm",'Product Line Summary'!D58,IF($B$6="InsureSight",'Product Line Summary'!D68,'Product Line Summary'!D78)))</f>
+        <v/>
+      </c>
+      <c r="E64" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!E48,IF($B$6="Affirm",'Product Line Summary'!E58,IF($B$6="InsureSight",'Product Line Summary'!E68,'Product Line Summary'!E78)))</f>
+        <v/>
+      </c>
+      <c r="F64" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!F48,IF($B$6="Affirm",'Product Line Summary'!F58,IF($B$6="InsureSight",'Product Line Summary'!F68,'Product Line Summary'!F78)))</f>
+        <v/>
+      </c>
+      <c r="G64" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!G48,IF($B$6="Affirm",'Product Line Summary'!G58,IF($B$6="InsureSight",'Product Line Summary'!G68,'Product Line Summary'!G78)))</f>
+        <v/>
+      </c>
+      <c r="H64" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!H48,IF($B$6="Affirm",'Product Line Summary'!H58,IF($B$6="InsureSight",'Product Line Summary'!H68,'Product Line Summary'!H78)))</f>
+        <v/>
+      </c>
+      <c r="I64" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!I48,IF($B$6="Affirm",'Product Line Summary'!I58,IF($B$6="InsureSight",'Product Line Summary'!I68,'Product Line Summary'!I78)))</f>
+        <v/>
+      </c>
+      <c r="J64" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!J48,IF($B$6="Affirm",'Product Line Summary'!J58,IF($B$6="InsureSight",'Product Line Summary'!J68,'Product Line Summary'!J78)))</f>
+        <v/>
+      </c>
+      <c r="K64" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!K48,IF($B$6="Affirm",'Product Line Summary'!K58,IF($B$6="InsureSight",'Product Line Summary'!K68,'Product Line Summary'!K78)))</f>
+        <v/>
+      </c>
+      <c r="L64" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!L48,IF($B$6="Affirm",'Product Line Summary'!L58,IF($B$6="InsureSight",'Product Line Summary'!L68,'Product Line Summary'!L78)))</f>
+        <v/>
+      </c>
+      <c r="M64" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!M48,IF($B$6="Affirm",'Product Line Summary'!M58,IF($B$6="InsureSight",'Product Line Summary'!M68,'Product Line Summary'!M78)))</f>
+        <v/>
+      </c>
+      <c r="N64" s="105">
+        <f>SUM(B64:M64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="102" t="inlineStr">
+        <is>
+          <t>Product Management</t>
+        </is>
+      </c>
+      <c r="B65" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!B49,IF($B$6="Affirm",'Product Line Summary'!B59,IF($B$6="InsureSight",'Product Line Summary'!B69,'Product Line Summary'!B79)))</f>
+        <v/>
+      </c>
+      <c r="C65" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!C49,IF($B$6="Affirm",'Product Line Summary'!C59,IF($B$6="InsureSight",'Product Line Summary'!C69,'Product Line Summary'!C79)))</f>
+        <v/>
+      </c>
+      <c r="D65" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!D49,IF($B$6="Affirm",'Product Line Summary'!D59,IF($B$6="InsureSight",'Product Line Summary'!D69,'Product Line Summary'!D79)))</f>
+        <v/>
+      </c>
+      <c r="E65" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!E49,IF($B$6="Affirm",'Product Line Summary'!E59,IF($B$6="InsureSight",'Product Line Summary'!E69,'Product Line Summary'!E79)))</f>
+        <v/>
+      </c>
+      <c r="F65" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!F49,IF($B$6="Affirm",'Product Line Summary'!F59,IF($B$6="InsureSight",'Product Line Summary'!F69,'Product Line Summary'!F79)))</f>
+        <v/>
+      </c>
+      <c r="G65" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!G49,IF($B$6="Affirm",'Product Line Summary'!G59,IF($B$6="InsureSight",'Product Line Summary'!G69,'Product Line Summary'!G79)))</f>
+        <v/>
+      </c>
+      <c r="H65" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!H49,IF($B$6="Affirm",'Product Line Summary'!H59,IF($B$6="InsureSight",'Product Line Summary'!H69,'Product Line Summary'!H79)))</f>
+        <v/>
+      </c>
+      <c r="I65" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!I49,IF($B$6="Affirm",'Product Line Summary'!I59,IF($B$6="InsureSight",'Product Line Summary'!I69,'Product Line Summary'!I79)))</f>
+        <v/>
+      </c>
+      <c r="J65" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!J49,IF($B$6="Affirm",'Product Line Summary'!J59,IF($B$6="InsureSight",'Product Line Summary'!J69,'Product Line Summary'!J79)))</f>
+        <v/>
+      </c>
+      <c r="K65" s="104">
+        <f>IF($B$6="iGO",'Product Line Summary'!K49,IF($B$6="Affirm",'Product Line Summary'!K59,IF($B$6="InsureSight",'Product Line Summary'!K69,'Product Line Summary'!K79)))</f>
+        <v/>
+      </c>
+      <c r="L65" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!L49,IF($B$6="Affirm",'Product Line Summary'!L59,IF($B$6="InsureSight",'Product Line Summary'!L69,'Product Line Summary'!L79)))</f>
+        <v/>
+      </c>
+      <c r="M65" s="105">
+        <f>IF($B$6="iGO",'Product Line Summary'!M49,IF($B$6="Affirm",'Product Line Summary'!M59,IF($B$6="InsureSight",'Product Line Summary'!M69,'Product Line Summary'!M79)))</f>
+        <v/>
+      </c>
+      <c r="N65" s="105">
+        <f>SUM(B65:M65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="96" t="n"/>
+      <c r="B66" s="96" t="n"/>
+      <c r="C66" s="96" t="n"/>
+      <c r="D66" s="96" t="n"/>
+      <c r="E66" s="96" t="n"/>
+      <c r="F66" s="96" t="n"/>
+      <c r="G66" s="96" t="n"/>
+      <c r="H66" s="96" t="n"/>
+      <c r="I66" s="96" t="n"/>
+      <c r="J66" s="96" t="n"/>
+      <c r="K66" s="96" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="102" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B67" s="102" t="inlineStr">
+        <is>
+          <t>FY Revenue</t>
+        </is>
+      </c>
+      <c r="C67" s="102" t="inlineStr">
+        <is>
+          <t>FY COGS</t>
+        </is>
+      </c>
+      <c r="D67" s="102" t="inlineStr">
+        <is>
+          <t>FY CM$</t>
+        </is>
+      </c>
+      <c r="E67" s="96" t="n"/>
+      <c r="F67" s="96" t="n"/>
+      <c r="G67" s="96" t="n"/>
+      <c r="H67" s="96" t="n"/>
+      <c r="I67" s="96" t="n"/>
+      <c r="J67" s="96" t="n"/>
+      <c r="K67" s="96" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="102" t="inlineStr">
+        <is>
+          <t>iGO</t>
+        </is>
+      </c>
+      <c r="B68" s="104">
+        <f>'Product Line Summary'!R8</f>
+        <v/>
+      </c>
+      <c r="C68" s="104">
+        <f>'Product Line Summary'!R9</f>
+        <v/>
+      </c>
+      <c r="D68" s="104">
+        <f>'Product Line Summary'!R10</f>
+        <v/>
+      </c>
+      <c r="E68" s="96" t="n"/>
+      <c r="F68" s="96" t="n"/>
+      <c r="G68" s="96" t="n"/>
+      <c r="H68" s="96" t="n"/>
+      <c r="I68" s="96" t="n"/>
+      <c r="J68" s="96" t="n"/>
+      <c r="K68" s="96" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="102" t="inlineStr">
+        <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="B69" s="104">
+        <f>'Product Line Summary'!R16</f>
+        <v/>
+      </c>
+      <c r="C69" s="104">
+        <f>'Product Line Summary'!R17</f>
+        <v/>
+      </c>
+      <c r="D69" s="104">
+        <f>'Product Line Summary'!R18</f>
+        <v/>
+      </c>
+      <c r="E69" s="96" t="n"/>
+      <c r="F69" s="96" t="n"/>
+      <c r="G69" s="96" t="n"/>
+      <c r="H69" s="96" t="n"/>
+      <c r="I69" s="96" t="n"/>
+      <c r="J69" s="96" t="n"/>
+      <c r="K69" s="96" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="102" t="inlineStr">
+        <is>
+          <t>InsureSight</t>
+        </is>
+      </c>
+      <c r="B70" s="104">
+        <f>'Product Line Summary'!R24</f>
+        <v/>
+      </c>
+      <c r="C70" s="104">
+        <f>'Product Line Summary'!R25</f>
+        <v/>
+      </c>
+      <c r="D70" s="104">
+        <f>'Product Line Summary'!R26</f>
+        <v/>
+      </c>
+      <c r="E70" s="96" t="n"/>
+      <c r="F70" s="96" t="n"/>
+      <c r="G70" s="96" t="n"/>
+      <c r="H70" s="96" t="n"/>
+      <c r="I70" s="96" t="n"/>
+      <c r="J70" s="96" t="n"/>
+      <c r="K70" s="96" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="102" t="inlineStr">
+        <is>
+          <t>DocFast</t>
+        </is>
+      </c>
+      <c r="B71" s="104">
+        <f>'Product Line Summary'!R32</f>
+        <v/>
+      </c>
+      <c r="C71" s="104">
+        <f>'Product Line Summary'!R33</f>
+        <v/>
+      </c>
+      <c r="D71" s="104">
+        <f>'Product Line Summary'!R34</f>
+        <v/>
+      </c>
+      <c r="E71" s="96" t="n"/>
+      <c r="F71" s="96" t="n"/>
+      <c r="G71" s="96" t="n"/>
+      <c r="H71" s="96" t="n"/>
+      <c r="I71" s="96" t="n"/>
+      <c r="J71" s="96" t="n"/>
+      <c r="K71" s="96" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="96" t="n"/>
+      <c r="B72" s="96" t="n"/>
+      <c r="C72" s="96" t="n"/>
+      <c r="D72" s="96" t="n"/>
+      <c r="E72" s="96" t="n"/>
+      <c r="F72" s="96" t="n"/>
+      <c r="G72" s="96" t="n"/>
+      <c r="H72" s="96" t="n"/>
+      <c r="I72" s="96" t="n"/>
+      <c r="J72" s="96" t="n"/>
+      <c r="K72" s="96" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="102" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B73" s="102" t="inlineStr">
+        <is>
+          <t>iGO</t>
+        </is>
+      </c>
+      <c r="C73" s="102" t="inlineStr">
+        <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="D73" s="102" t="inlineStr">
+        <is>
+          <t>InsureSight</t>
+        </is>
+      </c>
+      <c r="E73" s="102" t="inlineStr">
+        <is>
+          <t>DocFast</t>
+        </is>
+      </c>
+      <c r="F73" s="96" t="n"/>
+      <c r="G73" s="96" t="n"/>
+      <c r="H73" s="96" t="n"/>
+      <c r="I73" s="96" t="n"/>
+      <c r="J73" s="96" t="n"/>
+      <c r="K73" s="96" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="102" t="inlineStr">
+        <is>
+          <t>NetOps</t>
+        </is>
+      </c>
+      <c r="B74" s="104">
+        <f>'Product Line Summary'!R43</f>
+        <v/>
+      </c>
+      <c r="C74" s="104">
+        <f>'Product Line Summary'!R53</f>
+        <v/>
+      </c>
+      <c r="D74" s="104">
+        <f>'Product Line Summary'!R63</f>
+        <v/>
+      </c>
+      <c r="E74" s="104">
+        <f>'Product Line Summary'!R73</f>
+        <v/>
+      </c>
+      <c r="F74" s="96" t="n"/>
+      <c r="G74" s="96" t="n"/>
+      <c r="H74" s="96" t="n"/>
+      <c r="I74" s="96" t="n"/>
+      <c r="J74" s="96" t="n"/>
+      <c r="K74" s="96" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="102" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B75" s="104">
+        <f>'Product Line Summary'!R44</f>
+        <v/>
+      </c>
+      <c r="C75" s="104">
+        <f>'Product Line Summary'!R54</f>
+        <v/>
+      </c>
+      <c r="D75" s="104">
+        <f>'Product Line Summary'!R64</f>
+        <v/>
+      </c>
+      <c r="E75" s="104">
+        <f>'Product Line Summary'!R74</f>
+        <v/>
+      </c>
+      <c r="F75" s="96" t="n"/>
+      <c r="G75" s="96" t="n"/>
+      <c r="H75" s="96" t="n"/>
+      <c r="I75" s="96" t="n"/>
+      <c r="J75" s="96" t="n"/>
+      <c r="K75" s="96" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="102" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="B76" s="104">
+        <f>'Product Line Summary'!R45</f>
+        <v/>
+      </c>
+      <c r="C76" s="104">
+        <f>'Product Line Summary'!R55</f>
+        <v/>
+      </c>
+      <c r="D76" s="104">
+        <f>'Product Line Summary'!R65</f>
+        <v/>
+      </c>
+      <c r="E76" s="104">
+        <f>'Product Line Summary'!R75</f>
+        <v/>
+      </c>
+      <c r="F76" s="96" t="n"/>
+      <c r="G76" s="96" t="n"/>
+      <c r="H76" s="96" t="n"/>
+      <c r="I76" s="96" t="n"/>
+      <c r="J76" s="96" t="n"/>
+      <c r="K76" s="96" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="102" t="inlineStr">
+        <is>
+          <t>Partners</t>
+        </is>
+      </c>
+      <c r="B77" s="104">
+        <f>'Product Line Summary'!R46</f>
+        <v/>
+      </c>
+      <c r="C77" s="104">
+        <f>'Product Line Summary'!R56</f>
+        <v/>
+      </c>
+      <c r="D77" s="104">
+        <f>'Product Line Summary'!R66</f>
+        <v/>
+      </c>
+      <c r="E77" s="104">
+        <f>'Product Line Summary'!R76</f>
+        <v/>
+      </c>
+      <c r="F77" s="96" t="n"/>
+      <c r="G77" s="96" t="n"/>
+      <c r="H77" s="96" t="n"/>
+      <c r="I77" s="96" t="n"/>
+      <c r="J77" s="96" t="n"/>
+      <c r="K77" s="96" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="102" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="B78" s="104">
+        <f>'Product Line Summary'!R47</f>
+        <v/>
+      </c>
+      <c r="C78" s="104">
+        <f>'Product Line Summary'!R57</f>
+        <v/>
+      </c>
+      <c r="D78" s="104">
+        <f>'Product Line Summary'!R67</f>
+        <v/>
+      </c>
+      <c r="E78" s="104">
+        <f>'Product Line Summary'!R77</f>
+        <v/>
+      </c>
+      <c r="F78" s="96" t="n"/>
+      <c r="G78" s="96" t="n"/>
+      <c r="H78" s="96" t="n"/>
+      <c r="I78" s="96" t="n"/>
+      <c r="J78" s="96" t="n"/>
+      <c r="K78" s="96" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="102" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="B79" s="104">
+        <f>'Product Line Summary'!R48</f>
+        <v/>
+      </c>
+      <c r="C79" s="104">
+        <f>'Product Line Summary'!R58</f>
+        <v/>
+      </c>
+      <c r="D79" s="104">
+        <f>'Product Line Summary'!R68</f>
+        <v/>
+      </c>
+      <c r="E79" s="104">
+        <f>'Product Line Summary'!R78</f>
+        <v/>
+      </c>
+      <c r="F79" s="96" t="n"/>
+      <c r="G79" s="96" t="n"/>
+      <c r="H79" s="96" t="n"/>
+      <c r="I79" s="96" t="n"/>
+      <c r="J79" s="96" t="n"/>
+      <c r="K79" s="96" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="102" t="inlineStr">
+        <is>
+          <t>Product Mgmt</t>
+        </is>
+      </c>
+      <c r="B80" s="104">
+        <f>'Product Line Summary'!R49</f>
+        <v/>
+      </c>
+      <c r="C80" s="104">
+        <f>'Product Line Summary'!R59</f>
+        <v/>
+      </c>
+      <c r="D80" s="104">
+        <f>'Product Line Summary'!R69</f>
+        <v/>
+      </c>
+      <c r="E80" s="104">
+        <f>'Product Line Summary'!R79</f>
+        <v/>
+      </c>
+      <c r="F80" s="96" t="n"/>
+      <c r="G80" s="96" t="n"/>
+      <c r="H80" s="96" t="n"/>
+      <c r="I80" s="96" t="n"/>
+      <c r="J80" s="96" t="n"/>
+      <c r="K80" s="96" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="96" t="n"/>
+      <c r="B81" s="96" t="n"/>
+      <c r="C81" s="96" t="n"/>
+      <c r="D81" s="96" t="n"/>
+      <c r="E81" s="96" t="n"/>
+      <c r="F81" s="96" t="n"/>
+      <c r="G81" s="96" t="n"/>
+      <c r="H81" s="96" t="n"/>
+      <c r="I81" s="96" t="n"/>
+      <c r="J81" s="96" t="n"/>
+      <c r="K81" s="96" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="102" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B82" s="102" t="inlineStr">
+        <is>
+          <t>iGO</t>
+        </is>
+      </c>
+      <c r="C82" s="102" t="inlineStr">
+        <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="D82" s="102" t="inlineStr">
+        <is>
+          <t>InsureSight</t>
+        </is>
+      </c>
+      <c r="E82" s="102" t="inlineStr">
+        <is>
+          <t>DocFast</t>
+        </is>
+      </c>
+      <c r="F82" s="96" t="n"/>
+      <c r="G82" s="96" t="n"/>
+      <c r="H82" s="96" t="n"/>
+      <c r="I82" s="96" t="n"/>
+      <c r="J82" s="96" t="n"/>
+      <c r="K82" s="96" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="102" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="B83" s="104">
+        <f>'Product Line Summary'!B8</f>
+        <v/>
+      </c>
+      <c r="C83" s="104">
+        <f>'Product Line Summary'!B16</f>
+        <v/>
+      </c>
+      <c r="D83" s="104">
+        <f>'Product Line Summary'!B24</f>
+        <v/>
+      </c>
+      <c r="E83" s="104">
+        <f>'Product Line Summary'!B32</f>
+        <v/>
+      </c>
+      <c r="F83" s="96" t="n"/>
+      <c r="G83" s="96" t="n"/>
+      <c r="H83" s="96" t="n"/>
+      <c r="I83" s="96" t="n"/>
+      <c r="J83" s="96" t="n"/>
+      <c r="K83" s="96" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="102" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="B84" s="104">
+        <f>'Product Line Summary'!C8</f>
+        <v/>
+      </c>
+      <c r="C84" s="104">
+        <f>'Product Line Summary'!C16</f>
+        <v/>
+      </c>
+      <c r="D84" s="104">
+        <f>'Product Line Summary'!C24</f>
+        <v/>
+      </c>
+      <c r="E84" s="104">
+        <f>'Product Line Summary'!C32</f>
+        <v/>
+      </c>
+      <c r="F84" s="96" t="n"/>
+      <c r="G84" s="96" t="n"/>
+      <c r="H84" s="96" t="n"/>
+      <c r="I84" s="96" t="n"/>
+      <c r="J84" s="96" t="n"/>
+      <c r="K84" s="96" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="102" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="B85" s="104">
+        <f>'Product Line Summary'!D8</f>
+        <v/>
+      </c>
+      <c r="C85" s="104">
+        <f>'Product Line Summary'!D16</f>
+        <v/>
+      </c>
+      <c r="D85" s="104">
+        <f>'Product Line Summary'!D24</f>
+        <v/>
+      </c>
+      <c r="E85" s="104">
+        <f>'Product Line Summary'!D32</f>
+        <v/>
+      </c>
+      <c r="F85" s="96" t="n"/>
+      <c r="G85" s="96" t="n"/>
+      <c r="H85" s="96" t="n"/>
+      <c r="I85" s="96" t="n"/>
+      <c r="J85" s="96" t="n"/>
+      <c r="K85" s="96" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="102" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="B86" s="104">
+        <f>'Product Line Summary'!E8</f>
+        <v/>
+      </c>
+      <c r="C86" s="104">
+        <f>'Product Line Summary'!E16</f>
+        <v/>
+      </c>
+      <c r="D86" s="104">
+        <f>'Product Line Summary'!E24</f>
+        <v/>
+      </c>
+      <c r="E86" s="104">
+        <f>'Product Line Summary'!E32</f>
+        <v/>
+      </c>
+      <c r="F86" s="96" t="n"/>
+      <c r="G86" s="96" t="n"/>
+      <c r="H86" s="96" t="n"/>
+      <c r="I86" s="96" t="n"/>
+      <c r="J86" s="96" t="n"/>
+      <c r="K86" s="96" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="102" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B87" s="104">
+        <f>'Product Line Summary'!F8</f>
+        <v/>
+      </c>
+      <c r="C87" s="104">
+        <f>'Product Line Summary'!F16</f>
+        <v/>
+      </c>
+      <c r="D87" s="104">
+        <f>'Product Line Summary'!F24</f>
+        <v/>
+      </c>
+      <c r="E87" s="104">
+        <f>'Product Line Summary'!F32</f>
+        <v/>
+      </c>
+      <c r="F87" s="96" t="n"/>
+      <c r="G87" s="96" t="n"/>
+      <c r="H87" s="96" t="n"/>
+      <c r="I87" s="96" t="n"/>
+      <c r="J87" s="96" t="n"/>
+      <c r="K87" s="96" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="102" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B88" s="104">
+        <f>'Product Line Summary'!G8</f>
+        <v/>
+      </c>
+      <c r="C88" s="104">
+        <f>'Product Line Summary'!G16</f>
+        <v/>
+      </c>
+      <c r="D88" s="104">
+        <f>'Product Line Summary'!G24</f>
+        <v/>
+      </c>
+      <c r="E88" s="104">
+        <f>'Product Line Summary'!G32</f>
+        <v/>
+      </c>
+      <c r="F88" s="96" t="n"/>
+      <c r="G88" s="96" t="n"/>
+      <c r="H88" s="96" t="n"/>
+      <c r="I88" s="96" t="n"/>
+      <c r="J88" s="96" t="n"/>
+      <c r="K88" s="96" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="102" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B89" s="104">
+        <f>'Product Line Summary'!H8</f>
+        <v/>
+      </c>
+      <c r="C89" s="104">
+        <f>'Product Line Summary'!H16</f>
+        <v/>
+      </c>
+      <c r="D89" s="104">
+        <f>'Product Line Summary'!H24</f>
+        <v/>
+      </c>
+      <c r="E89" s="104">
+        <f>'Product Line Summary'!H32</f>
+        <v/>
+      </c>
+      <c r="F89" s="96" t="n"/>
+      <c r="G89" s="96" t="n"/>
+      <c r="H89" s="96" t="n"/>
+      <c r="I89" s="96" t="n"/>
+      <c r="J89" s="96" t="n"/>
+      <c r="K89" s="96" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="102" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B90" s="104">
+        <f>'Product Line Summary'!I8</f>
+        <v/>
+      </c>
+      <c r="C90" s="104">
+        <f>'Product Line Summary'!I16</f>
+        <v/>
+      </c>
+      <c r="D90" s="104">
+        <f>'Product Line Summary'!I24</f>
+        <v/>
+      </c>
+      <c r="E90" s="104">
+        <f>'Product Line Summary'!I32</f>
+        <v/>
+      </c>
+      <c r="F90" s="96" t="n"/>
+      <c r="G90" s="96" t="n"/>
+      <c r="H90" s="96" t="n"/>
+      <c r="I90" s="96" t="n"/>
+      <c r="J90" s="96" t="n"/>
+      <c r="K90" s="96" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="102" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B91" s="104">
+        <f>'Product Line Summary'!J8</f>
+        <v/>
+      </c>
+      <c r="C91" s="104">
+        <f>'Product Line Summary'!J16</f>
+        <v/>
+      </c>
+      <c r="D91" s="104">
+        <f>'Product Line Summary'!J24</f>
+        <v/>
+      </c>
+      <c r="E91" s="104">
+        <f>'Product Line Summary'!J32</f>
+        <v/>
+      </c>
+      <c r="F91" s="96" t="n"/>
+      <c r="G91" s="96" t="n"/>
+      <c r="H91" s="96" t="n"/>
+      <c r="I91" s="96" t="n"/>
+      <c r="J91" s="96" t="n"/>
+      <c r="K91" s="96" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="102" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B92" s="104">
+        <f>'Product Line Summary'!K8</f>
+        <v/>
+      </c>
+      <c r="C92" s="104">
+        <f>'Product Line Summary'!K16</f>
+        <v/>
+      </c>
+      <c r="D92" s="104">
+        <f>'Product Line Summary'!K24</f>
+        <v/>
+      </c>
+      <c r="E92" s="104">
+        <f>'Product Line Summary'!K32</f>
+        <v/>
+      </c>
+      <c r="F92" s="96" t="n"/>
+      <c r="G92" s="96" t="n"/>
+      <c r="H92" s="96" t="n"/>
+      <c r="I92" s="96" t="n"/>
+      <c r="J92" s="96" t="n"/>
+      <c r="K92" s="96" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="102" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B93" s="104">
+        <f>'Product Line Summary'!L8</f>
+        <v/>
+      </c>
+      <c r="C93" s="104">
+        <f>'Product Line Summary'!L16</f>
+        <v/>
+      </c>
+      <c r="D93" s="104">
+        <f>'Product Line Summary'!L24</f>
+        <v/>
+      </c>
+      <c r="E93" s="104">
+        <f>'Product Line Summary'!L32</f>
+        <v/>
+      </c>
+      <c r="F93" s="96" t="n"/>
+      <c r="G93" s="96" t="n"/>
+      <c r="H93" s="96" t="n"/>
+      <c r="I93" s="96" t="n"/>
+      <c r="J93" s="96" t="n"/>
+      <c r="K93" s="96" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="102" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="B94" s="104">
+        <f>'Product Line Summary'!M8</f>
+        <v/>
+      </c>
+      <c r="C94" s="104">
+        <f>'Product Line Summary'!M16</f>
+        <v/>
+      </c>
+      <c r="D94" s="104">
+        <f>'Product Line Summary'!M24</f>
+        <v/>
+      </c>
+      <c r="E94" s="104">
+        <f>'Product Line Summary'!M32</f>
+        <v/>
+      </c>
+      <c r="F94" s="96" t="n"/>
+      <c r="G94" s="96" t="n"/>
+      <c r="H94" s="96" t="n"/>
+      <c r="I94" s="96" t="n"/>
+      <c r="J94" s="96" t="n"/>
+      <c r="K94" s="96" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="96" t="n"/>
+      <c r="B95" s="96" t="n"/>
+      <c r="C95" s="96" t="n"/>
+      <c r="D95" s="96" t="n"/>
+      <c r="E95" s="96" t="n"/>
+      <c r="F95" s="96" t="n"/>
+      <c r="G95" s="96" t="n"/>
+      <c r="H95" s="96" t="n"/>
+      <c r="I95" s="96" t="n"/>
+      <c r="J95" s="96" t="n"/>
+      <c r="K95" s="96" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="102" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B96" s="102" t="inlineStr">
+        <is>
+          <t>iGO</t>
+        </is>
+      </c>
+      <c r="C96" s="102" t="inlineStr">
+        <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="D96" s="102" t="inlineStr">
+        <is>
+          <t>InsureSight</t>
+        </is>
+      </c>
+      <c r="E96" s="102" t="inlineStr">
+        <is>
+          <t>DocFast</t>
+        </is>
+      </c>
+      <c r="F96" s="96" t="n"/>
+      <c r="G96" s="96" t="n"/>
+      <c r="H96" s="96" t="n"/>
+      <c r="I96" s="96" t="n"/>
+      <c r="J96" s="96" t="n"/>
+      <c r="K96" s="96" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="102" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="B97" s="106">
+        <f>'Product Line Summary'!B11</f>
+        <v/>
+      </c>
+      <c r="C97" s="106">
+        <f>'Product Line Summary'!B19</f>
+        <v/>
+      </c>
+      <c r="D97" s="106">
+        <f>'Product Line Summary'!B27</f>
+        <v/>
+      </c>
+      <c r="E97" s="106">
+        <f>'Product Line Summary'!B35</f>
+        <v/>
+      </c>
+      <c r="F97" s="96" t="n"/>
+      <c r="G97" s="96" t="n"/>
+      <c r="H97" s="96" t="n"/>
+      <c r="I97" s="96" t="n"/>
+      <c r="J97" s="96" t="n"/>
+      <c r="K97" s="96" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="102" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="B98" s="106">
+        <f>'Product Line Summary'!C11</f>
+        <v/>
+      </c>
+      <c r="C98" s="106">
+        <f>'Product Line Summary'!C19</f>
+        <v/>
+      </c>
+      <c r="D98" s="106">
+        <f>'Product Line Summary'!C27</f>
+        <v/>
+      </c>
+      <c r="E98" s="106">
+        <f>'Product Line Summary'!C35</f>
+        <v/>
+      </c>
+      <c r="F98" s="96" t="n"/>
+      <c r="G98" s="96" t="n"/>
+      <c r="H98" s="96" t="n"/>
+      <c r="I98" s="96" t="n"/>
+      <c r="J98" s="96" t="n"/>
+      <c r="K98" s="96" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="102" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="B99" s="106">
+        <f>'Product Line Summary'!D11</f>
+        <v/>
+      </c>
+      <c r="C99" s="106">
+        <f>'Product Line Summary'!D19</f>
+        <v/>
+      </c>
+      <c r="D99" s="106">
+        <f>'Product Line Summary'!D27</f>
+        <v/>
+      </c>
+      <c r="E99" s="106">
+        <f>'Product Line Summary'!D35</f>
+        <v/>
+      </c>
+      <c r="F99" s="96" t="n"/>
+      <c r="G99" s="96" t="n"/>
+      <c r="H99" s="96" t="n"/>
+      <c r="I99" s="96" t="n"/>
+      <c r="J99" s="96" t="n"/>
+      <c r="K99" s="96" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="102" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="B100" s="106">
+        <f>'Product Line Summary'!E11</f>
+        <v/>
+      </c>
+      <c r="C100" s="106">
+        <f>'Product Line Summary'!E19</f>
+        <v/>
+      </c>
+      <c r="D100" s="106">
+        <f>'Product Line Summary'!E27</f>
+        <v/>
+      </c>
+      <c r="E100" s="106">
+        <f>'Product Line Summary'!E35</f>
+        <v/>
+      </c>
+      <c r="F100" s="96" t="n"/>
+      <c r="G100" s="96" t="n"/>
+      <c r="H100" s="96" t="n"/>
+      <c r="I100" s="96" t="n"/>
+      <c r="J100" s="96" t="n"/>
+      <c r="K100" s="96" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="102" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B101" s="106">
+        <f>'Product Line Summary'!F11</f>
+        <v/>
+      </c>
+      <c r="C101" s="106">
+        <f>'Product Line Summary'!F19</f>
+        <v/>
+      </c>
+      <c r="D101" s="106">
+        <f>'Product Line Summary'!F27</f>
+        <v/>
+      </c>
+      <c r="E101" s="106">
+        <f>'Product Line Summary'!F35</f>
+        <v/>
+      </c>
+      <c r="F101" s="96" t="n"/>
+      <c r="G101" s="96" t="n"/>
+      <c r="H101" s="96" t="n"/>
+      <c r="I101" s="96" t="n"/>
+      <c r="J101" s="96" t="n"/>
+      <c r="K101" s="96" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="102" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B102" s="106">
+        <f>'Product Line Summary'!G11</f>
+        <v/>
+      </c>
+      <c r="C102" s="106">
+        <f>'Product Line Summary'!G19</f>
+        <v/>
+      </c>
+      <c r="D102" s="106">
+        <f>'Product Line Summary'!G27</f>
+        <v/>
+      </c>
+      <c r="E102" s="106">
+        <f>'Product Line Summary'!G35</f>
+        <v/>
+      </c>
+      <c r="F102" s="96" t="n"/>
+      <c r="G102" s="96" t="n"/>
+      <c r="H102" s="96" t="n"/>
+      <c r="I102" s="96" t="n"/>
+      <c r="J102" s="96" t="n"/>
+      <c r="K102" s="96" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="102" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B103" s="106">
+        <f>'Product Line Summary'!H11</f>
+        <v/>
+      </c>
+      <c r="C103" s="106">
+        <f>'Product Line Summary'!H19</f>
+        <v/>
+      </c>
+      <c r="D103" s="106">
+        <f>'Product Line Summary'!H27</f>
+        <v/>
+      </c>
+      <c r="E103" s="106">
+        <f>'Product Line Summary'!H35</f>
+        <v/>
+      </c>
+      <c r="F103" s="96" t="n"/>
+      <c r="G103" s="96" t="n"/>
+      <c r="H103" s="96" t="n"/>
+      <c r="I103" s="96" t="n"/>
+      <c r="J103" s="96" t="n"/>
+      <c r="K103" s="96" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="102" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B104" s="106">
+        <f>'Product Line Summary'!I11</f>
+        <v/>
+      </c>
+      <c r="C104" s="106">
+        <f>'Product Line Summary'!I19</f>
+        <v/>
+      </c>
+      <c r="D104" s="106">
+        <f>'Product Line Summary'!I27</f>
+        <v/>
+      </c>
+      <c r="E104" s="106">
+        <f>'Product Line Summary'!I35</f>
+        <v/>
+      </c>
+      <c r="F104" s="96" t="n"/>
+      <c r="G104" s="96" t="n"/>
+      <c r="H104" s="96" t="n"/>
+      <c r="I104" s="96" t="n"/>
+      <c r="J104" s="96" t="n"/>
+      <c r="K104" s="96" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="102" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B105" s="106">
+        <f>'Product Line Summary'!J11</f>
+        <v/>
+      </c>
+      <c r="C105" s="106">
+        <f>'Product Line Summary'!J19</f>
+        <v/>
+      </c>
+      <c r="D105" s="106">
+        <f>'Product Line Summary'!J27</f>
+        <v/>
+      </c>
+      <c r="E105" s="106">
+        <f>'Product Line Summary'!J35</f>
+        <v/>
+      </c>
+      <c r="F105" s="96" t="n"/>
+      <c r="G105" s="96" t="n"/>
+      <c r="H105" s="96" t="n"/>
+      <c r="I105" s="96" t="n"/>
+      <c r="J105" s="96" t="n"/>
+      <c r="K105" s="96" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="102" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B106" s="106">
+        <f>'Product Line Summary'!K11</f>
+        <v/>
+      </c>
+      <c r="C106" s="106">
+        <f>'Product Line Summary'!K19</f>
+        <v/>
+      </c>
+      <c r="D106" s="106">
+        <f>'Product Line Summary'!K27</f>
+        <v/>
+      </c>
+      <c r="E106" s="106">
+        <f>'Product Line Summary'!K35</f>
+        <v/>
+      </c>
+      <c r="F106" s="96" t="n"/>
+      <c r="G106" s="96" t="n"/>
+      <c r="H106" s="96" t="n"/>
+      <c r="I106" s="96" t="n"/>
+      <c r="J106" s="96" t="n"/>
+      <c r="K106" s="96" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="102" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B107" s="106">
+        <f>'Product Line Summary'!L11</f>
+        <v/>
+      </c>
+      <c r="C107" s="106">
+        <f>'Product Line Summary'!L19</f>
+        <v/>
+      </c>
+      <c r="D107" s="106">
+        <f>'Product Line Summary'!L27</f>
+        <v/>
+      </c>
+      <c r="E107" s="106">
+        <f>'Product Line Summary'!L35</f>
+        <v/>
+      </c>
+      <c r="F107" s="96" t="n"/>
+      <c r="G107" s="96" t="n"/>
+      <c r="H107" s="96" t="n"/>
+      <c r="I107" s="96" t="n"/>
+      <c r="J107" s="96" t="n"/>
+      <c r="K107" s="96" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="102" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="B108" s="106">
+        <f>'Product Line Summary'!M11</f>
+        <v/>
+      </c>
+      <c r="C108" s="106">
+        <f>'Product Line Summary'!M19</f>
+        <v/>
+      </c>
+      <c r="D108" s="106">
+        <f>'Product Line Summary'!M27</f>
+        <v/>
+      </c>
+      <c r="E108" s="106">
+        <f>'Product Line Summary'!M35</f>
+        <v/>
+      </c>
+      <c r="F108" s="96" t="n"/>
+      <c r="G108" s="96" t="n"/>
+      <c r="H108" s="96" t="n"/>
+      <c r="I108" s="96" t="n"/>
+      <c r="J108" s="96" t="n"/>
+      <c r="K108" s="96" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="96" t="n"/>
+      <c r="B109" s="96" t="n"/>
+      <c r="C109" s="96" t="n"/>
+      <c r="D109" s="96" t="n"/>
+      <c r="E109" s="96" t="n"/>
+      <c r="F109" s="96" t="n"/>
+      <c r="G109" s="96" t="n"/>
+      <c r="H109" s="96" t="n"/>
+      <c r="I109" s="96" t="n"/>
+      <c r="J109" s="96" t="n"/>
+      <c r="K109" s="96" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="102" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B110" s="102" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C110" s="102" t="inlineStr">
+        <is>
+          <t>Cost of Revenue</t>
+        </is>
+      </c>
+      <c r="D110" s="102" t="inlineStr">
+        <is>
+          <t>Contribution Margin</t>
+        </is>
+      </c>
+      <c r="E110" s="96" t="n"/>
+      <c r="F110" s="96" t="n"/>
+      <c r="G110" s="96" t="n"/>
+      <c r="H110" s="96" t="n"/>
+      <c r="I110" s="96" t="n"/>
+      <c r="J110" s="96" t="n"/>
+      <c r="K110" s="96" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="102" t="inlineStr">
+        <is>
+          <t>iGO</t>
+        </is>
+      </c>
+      <c r="B111" s="104">
+        <f>'Product Line Summary'!R8</f>
+        <v/>
+      </c>
+      <c r="C111" s="104">
+        <f>'Product Line Summary'!R9</f>
+        <v/>
+      </c>
+      <c r="D111" s="104">
+        <f>'Product Line Summary'!R10</f>
+        <v/>
+      </c>
+      <c r="E111" s="96" t="n"/>
+      <c r="F111" s="96" t="n"/>
+      <c r="G111" s="96" t="n"/>
+      <c r="H111" s="96" t="n"/>
+      <c r="I111" s="96" t="n"/>
+      <c r="J111" s="96" t="n"/>
+      <c r="K111" s="96" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="102" t="inlineStr">
+        <is>
+          <t>Affirm</t>
+        </is>
+      </c>
+      <c r="B112" s="104">
+        <f>'Product Line Summary'!R16</f>
+        <v/>
+      </c>
+      <c r="C112" s="104">
+        <f>'Product Line Summary'!R17</f>
+        <v/>
+      </c>
+      <c r="D112" s="104">
+        <f>'Product Line Summary'!R18</f>
+        <v/>
+      </c>
+      <c r="E112" s="96" t="n"/>
+      <c r="F112" s="96" t="n"/>
+      <c r="G112" s="96" t="n"/>
+      <c r="H112" s="96" t="n"/>
+      <c r="I112" s="96" t="n"/>
+      <c r="J112" s="96" t="n"/>
+      <c r="K112" s="96" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="102" t="inlineStr">
+        <is>
+          <t>InsureSight</t>
+        </is>
+      </c>
+      <c r="B113" s="104">
+        <f>'Product Line Summary'!R24</f>
+        <v/>
+      </c>
+      <c r="C113" s="104">
+        <f>'Product Line Summary'!R25</f>
+        <v/>
+      </c>
+      <c r="D113" s="104">
+        <f>'Product Line Summary'!R26</f>
+        <v/>
+      </c>
+      <c r="E113" s="96" t="n"/>
+      <c r="F113" s="96" t="n"/>
+      <c r="G113" s="96" t="n"/>
+      <c r="H113" s="96" t="n"/>
+      <c r="I113" s="96" t="n"/>
+      <c r="J113" s="96" t="n"/>
+      <c r="K113" s="96" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="102" t="inlineStr">
+        <is>
+          <t>DocFast</t>
+        </is>
+      </c>
+      <c r="B114" s="104">
+        <f>'Product Line Summary'!R32</f>
+        <v/>
+      </c>
+      <c r="C114" s="104">
+        <f>'Product Line Summary'!R33</f>
+        <v/>
+      </c>
+      <c r="D114" s="104">
+        <f>'Product Line Summary'!R34</f>
+        <v/>
+      </c>
+      <c r="E114" s="96" t="n"/>
+      <c r="F114" s="96" t="n"/>
+      <c r="G114" s="96" t="n"/>
+      <c r="H114" s="96" t="n"/>
+      <c r="I114" s="96" t="n"/>
+      <c r="J114" s="96" t="n"/>
+      <c r="K114" s="96" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="96" t="n"/>
+      <c r="B115" s="96" t="n"/>
+      <c r="C115" s="96" t="n"/>
+      <c r="D115" s="96" t="n"/>
+      <c r="E115" s="96" t="n"/>
+      <c r="F115" s="96" t="n"/>
+      <c r="G115" s="96" t="n"/>
+      <c r="H115" s="96" t="n"/>
+      <c r="I115" s="96" t="n"/>
+      <c r="J115" s="96" t="n"/>
+      <c r="K115" s="96" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="100" t="inlineStr">
+        <is>
+          <t>SECTION 3: ADVANCED ANALYTICS</t>
+        </is>
+      </c>
+      <c r="B116" s="95" t="n"/>
+      <c r="C116" s="95" t="n"/>
+      <c r="D116" s="95" t="n"/>
+      <c r="E116" s="95" t="n"/>
+      <c r="F116" s="95" t="n"/>
+      <c r="G116" s="95" t="n"/>
+      <c r="H116" s="95" t="n"/>
+      <c r="I116" s="96" t="n"/>
+      <c r="J116" s="96" t="n"/>
+      <c r="K116" s="96" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="96" t="n"/>
+      <c r="B117" s="96" t="n"/>
+      <c r="C117" s="96" t="n"/>
+      <c r="D117" s="96" t="n"/>
+      <c r="E117" s="96" t="n"/>
+      <c r="F117" s="96" t="n"/>
+      <c r="G117" s="96" t="n"/>
+      <c r="H117" s="96" t="n"/>
+      <c r="I117" s="96" t="n"/>
+      <c r="J117" s="96" t="n"/>
+      <c r="K117" s="96" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="96" t="n"/>
+      <c r="B118" s="96" t="n"/>
+      <c r="C118" s="96" t="n"/>
+      <c r="D118" s="96" t="n"/>
+      <c r="E118" s="96" t="n"/>
+      <c r="F118" s="96" t="n"/>
+      <c r="G118" s="96" t="n"/>
+      <c r="H118" s="96" t="n"/>
+      <c r="I118" s="96" t="n"/>
+      <c r="J118" s="96" t="n"/>
+      <c r="K118" s="96" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="96" t="n"/>
+      <c r="B119" s="96" t="n"/>
+      <c r="C119" s="96" t="n"/>
+      <c r="D119" s="96" t="n"/>
+      <c r="E119" s="96" t="n"/>
+      <c r="F119" s="96" t="n"/>
+      <c r="G119" s="96" t="n"/>
+      <c r="H119" s="96" t="n"/>
+      <c r="I119" s="96" t="n"/>
+      <c r="J119" s="96" t="n"/>
+      <c r="K119" s="96" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="96" t="n"/>
+      <c r="B120" s="96" t="n"/>
+      <c r="C120" s="96" t="n"/>
+      <c r="D120" s="96" t="n"/>
+      <c r="E120" s="96" t="n"/>
+      <c r="F120" s="96" t="n"/>
+      <c r="G120" s="96" t="n"/>
+      <c r="H120" s="96" t="n"/>
+      <c r="I120" s="96" t="n"/>
+      <c r="J120" s="96" t="n"/>
+      <c r="K120" s="96" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="96" t="n"/>
+      <c r="B121" s="96" t="n"/>
+      <c r="C121" s="96" t="n"/>
+      <c r="D121" s="96" t="n"/>
+      <c r="E121" s="96" t="n"/>
+      <c r="F121" s="96" t="n"/>
+      <c r="G121" s="96" t="n"/>
+      <c r="H121" s="96" t="n"/>
+      <c r="I121" s="96" t="n"/>
+      <c r="J121" s="96" t="n"/>
+      <c r="K121" s="96" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="96" t="n"/>
+      <c r="B122" s="96" t="n"/>
+      <c r="C122" s="96" t="n"/>
+      <c r="D122" s="96" t="n"/>
+      <c r="E122" s="96" t="n"/>
+      <c r="F122" s="96" t="n"/>
+      <c r="G122" s="96" t="n"/>
+      <c r="H122" s="96" t="n"/>
+      <c r="I122" s="96" t="n"/>
+      <c r="J122" s="96" t="n"/>
+      <c r="K122" s="96" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="96" t="n"/>
+      <c r="B123" s="96" t="n"/>
+      <c r="C123" s="96" t="n"/>
+      <c r="D123" s="96" t="n"/>
+      <c r="E123" s="96" t="n"/>
+      <c r="F123" s="96" t="n"/>
+      <c r="G123" s="96" t="n"/>
+      <c r="H123" s="96" t="n"/>
+      <c r="I123" s="96" t="n"/>
+      <c r="J123" s="96" t="n"/>
+      <c r="K123" s="96" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="96" t="n"/>
+      <c r="B124" s="96" t="n"/>
+      <c r="C124" s="96" t="n"/>
+      <c r="D124" s="96" t="n"/>
+      <c r="E124" s="96" t="n"/>
+      <c r="F124" s="96" t="n"/>
+      <c r="G124" s="96" t="n"/>
+      <c r="H124" s="96" t="n"/>
+      <c r="I124" s="96" t="n"/>
+      <c r="J124" s="96" t="n"/>
+      <c r="K124" s="96" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="96" t="n"/>
+      <c r="B125" s="96" t="n"/>
+      <c r="C125" s="96" t="n"/>
+      <c r="D125" s="96" t="n"/>
+      <c r="E125" s="96" t="n"/>
+      <c r="F125" s="96" t="n"/>
+      <c r="G125" s="96" t="n"/>
+      <c r="H125" s="96" t="n"/>
+      <c r="I125" s="96" t="n"/>
+      <c r="J125" s="96" t="n"/>
+      <c r="K125" s="96" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="96" t="n"/>
+      <c r="B126" s="96" t="n"/>
+      <c r="C126" s="96" t="n"/>
+      <c r="D126" s="96" t="n"/>
+      <c r="E126" s="96" t="n"/>
+      <c r="F126" s="96" t="n"/>
+      <c r="G126" s="96" t="n"/>
+      <c r="H126" s="96" t="n"/>
+      <c r="I126" s="96" t="n"/>
+      <c r="J126" s="96" t="n"/>
+      <c r="K126" s="96" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="96" t="n"/>
+      <c r="B127" s="96" t="n"/>
+      <c r="C127" s="96" t="n"/>
+      <c r="D127" s="96" t="n"/>
+      <c r="E127" s="96" t="n"/>
+      <c r="F127" s="96" t="n"/>
+      <c r="G127" s="96" t="n"/>
+      <c r="H127" s="96" t="n"/>
+      <c r="I127" s="96" t="n"/>
+      <c r="J127" s="96" t="n"/>
+      <c r="K127" s="96" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="96" t="n"/>
+      <c r="B128" s="96" t="n"/>
+      <c r="C128" s="96" t="n"/>
+      <c r="D128" s="96" t="n"/>
+      <c r="E128" s="96" t="n"/>
+      <c r="F128" s="96" t="n"/>
+      <c r="G128" s="96" t="n"/>
+      <c r="H128" s="96" t="n"/>
+      <c r="I128" s="96" t="n"/>
+      <c r="J128" s="96" t="n"/>
+      <c r="K128" s="96" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="96" t="n"/>
+      <c r="B129" s="96" t="n"/>
+      <c r="C129" s="96" t="n"/>
+      <c r="D129" s="96" t="n"/>
+      <c r="E129" s="96" t="n"/>
+      <c r="F129" s="96" t="n"/>
+      <c r="G129" s="96" t="n"/>
+      <c r="H129" s="96" t="n"/>
+      <c r="I129" s="96" t="n"/>
+      <c r="J129" s="96" t="n"/>
+      <c r="K129" s="96" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="96" t="n"/>
+      <c r="B130" s="96" t="n"/>
+      <c r="C130" s="96" t="n"/>
+      <c r="D130" s="96" t="n"/>
+      <c r="E130" s="96" t="n"/>
+      <c r="F130" s="96" t="n"/>
+      <c r="G130" s="96" t="n"/>
+      <c r="H130" s="96" t="n"/>
+      <c r="I130" s="96" t="n"/>
+      <c r="J130" s="96" t="n"/>
+      <c r="K130" s="96" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="96" t="n"/>
+      <c r="B131" s="96" t="n"/>
+      <c r="C131" s="96" t="n"/>
+      <c r="D131" s="96" t="n"/>
+      <c r="E131" s="96" t="n"/>
+      <c r="F131" s="96" t="n"/>
+      <c r="G131" s="96" t="n"/>
+      <c r="H131" s="96" t="n"/>
+      <c r="I131" s="96" t="n"/>
+      <c r="J131" s="96" t="n"/>
+      <c r="K131" s="96" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="96" t="n"/>
+      <c r="B132" s="96" t="n"/>
+      <c r="C132" s="96" t="n"/>
+      <c r="D132" s="96" t="n"/>
+      <c r="E132" s="96" t="n"/>
+      <c r="F132" s="96" t="n"/>
+      <c r="G132" s="96" t="n"/>
+      <c r="H132" s="96" t="n"/>
+      <c r="I132" s="96" t="n"/>
+      <c r="J132" s="96" t="n"/>
+      <c r="K132" s="96" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="96" t="n"/>
+      <c r="B133" s="96" t="n"/>
+      <c r="C133" s="96" t="n"/>
+      <c r="D133" s="96" t="n"/>
+      <c r="E133" s="96" t="n"/>
+      <c r="F133" s="96" t="n"/>
+      <c r="G133" s="96" t="n"/>
+      <c r="H133" s="96" t="n"/>
+      <c r="I133" s="96" t="n"/>
+      <c r="J133" s="96" t="n"/>
+      <c r="K133" s="96" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="96" t="n"/>
+      <c r="B134" s="96" t="n"/>
+      <c r="C134" s="96" t="n"/>
+      <c r="D134" s="96" t="n"/>
+      <c r="E134" s="96" t="n"/>
+      <c r="F134" s="96" t="n"/>
+      <c r="G134" s="96" t="n"/>
+      <c r="H134" s="96" t="n"/>
+      <c r="I134" s="96" t="n"/>
+      <c r="J134" s="96" t="n"/>
+      <c r="K134" s="96" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="96" t="n"/>
+      <c r="B135" s="96" t="n"/>
+      <c r="C135" s="96" t="n"/>
+      <c r="D135" s="96" t="n"/>
+      <c r="E135" s="96" t="n"/>
+      <c r="F135" s="96" t="n"/>
+      <c r="G135" s="96" t="n"/>
+      <c r="H135" s="96" t="n"/>
+      <c r="I135" s="96" t="n"/>
+      <c r="J135" s="96" t="n"/>
+      <c r="K135" s="96" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="96" t="n"/>
+      <c r="B136" s="96" t="n"/>
+      <c r="C136" s="96" t="n"/>
+      <c r="D136" s="96" t="n"/>
+      <c r="E136" s="96" t="n"/>
+      <c r="F136" s="96" t="n"/>
+      <c r="G136" s="96" t="n"/>
+      <c r="H136" s="96" t="n"/>
+      <c r="I136" s="96" t="n"/>
+      <c r="J136" s="96" t="n"/>
+      <c r="K136" s="96" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="96" t="n"/>
+      <c r="B137" s="96" t="n"/>
+      <c r="C137" s="96" t="n"/>
+      <c r="D137" s="96" t="n"/>
+      <c r="E137" s="96" t="n"/>
+      <c r="F137" s="96" t="n"/>
+      <c r="G137" s="96" t="n"/>
+      <c r="H137" s="96" t="n"/>
+      <c r="I137" s="96" t="n"/>
+      <c r="J137" s="96" t="n"/>
+      <c r="K137" s="96" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="96" t="n"/>
+      <c r="B138" s="96" t="n"/>
+      <c r="C138" s="96" t="n"/>
+      <c r="D138" s="96" t="n"/>
+      <c r="E138" s="96" t="n"/>
+      <c r="F138" s="96" t="n"/>
+      <c r="G138" s="96" t="n"/>
+      <c r="H138" s="96" t="n"/>
+      <c r="I138" s="96" t="n"/>
+      <c r="J138" s="96" t="n"/>
+      <c r="K138" s="96" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="96" t="n"/>
+      <c r="B139" s="96" t="n"/>
+      <c r="C139" s="96" t="n"/>
+      <c r="D139" s="96" t="n"/>
+      <c r="E139" s="96" t="n"/>
+      <c r="F139" s="96" t="n"/>
+      <c r="G139" s="96" t="n"/>
+      <c r="H139" s="96" t="n"/>
+      <c r="I139" s="96" t="n"/>
+      <c r="J139" s="96" t="n"/>
+      <c r="K139" s="96" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="96" t="n"/>
+      <c r="B140" s="96" t="n"/>
+      <c r="C140" s="96" t="n"/>
+      <c r="D140" s="96" t="n"/>
+      <c r="E140" s="96" t="n"/>
+      <c r="F140" s="96" t="n"/>
+      <c r="G140" s="96" t="n"/>
+      <c r="H140" s="96" t="n"/>
+      <c r="I140" s="96" t="n"/>
+      <c r="J140" s="96" t="n"/>
+      <c r="K140" s="96" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="96" t="n"/>
+      <c r="B141" s="96" t="n"/>
+      <c r="C141" s="96" t="n"/>
+      <c r="D141" s="96" t="n"/>
+      <c r="E141" s="96" t="n"/>
+      <c r="F141" s="96" t="n"/>
+      <c r="G141" s="96" t="n"/>
+      <c r="H141" s="96" t="n"/>
+      <c r="I141" s="96" t="n"/>
+      <c r="J141" s="96" t="n"/>
+      <c r="K141" s="96" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="96" t="n"/>
+      <c r="B142" s="96" t="n"/>
+      <c r="C142" s="96" t="n"/>
+      <c r="D142" s="96" t="n"/>
+      <c r="E142" s="96" t="n"/>
+      <c r="F142" s="96" t="n"/>
+      <c r="G142" s="96" t="n"/>
+      <c r="H142" s="96" t="n"/>
+      <c r="I142" s="96" t="n"/>
+      <c r="J142" s="96" t="n"/>
+      <c r="K142" s="96" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="96" t="n"/>
+      <c r="B143" s="96" t="n"/>
+      <c r="C143" s="96" t="n"/>
+      <c r="D143" s="96" t="n"/>
+      <c r="E143" s="96" t="n"/>
+      <c r="F143" s="96" t="n"/>
+      <c r="G143" s="96" t="n"/>
+      <c r="H143" s="96" t="n"/>
+      <c r="I143" s="96" t="n"/>
+      <c r="J143" s="96" t="n"/>
+      <c r="K143" s="96" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="96" t="n"/>
+      <c r="B144" s="96" t="n"/>
+      <c r="C144" s="96" t="n"/>
+      <c r="D144" s="96" t="n"/>
+      <c r="E144" s="96" t="n"/>
+      <c r="F144" s="96" t="n"/>
+      <c r="G144" s="96" t="n"/>
+      <c r="H144" s="96" t="n"/>
+      <c r="I144" s="96" t="n"/>
+      <c r="J144" s="96" t="n"/>
+      <c r="K144" s="96" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="96" t="n"/>
+      <c r="B145" s="96" t="n"/>
+      <c r="C145" s="96" t="n"/>
+      <c r="D145" s="96" t="n"/>
+      <c r="E145" s="96" t="n"/>
+      <c r="F145" s="96" t="n"/>
+      <c r="G145" s="96" t="n"/>
+      <c r="H145" s="96" t="n"/>
+      <c r="I145" s="96" t="n"/>
+      <c r="J145" s="96" t="n"/>
+      <c r="K145" s="96" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="96" t="n"/>
+      <c r="B146" s="96" t="n"/>
+      <c r="C146" s="96" t="n"/>
+      <c r="D146" s="96" t="n"/>
+      <c r="E146" s="96" t="n"/>
+      <c r="F146" s="96" t="n"/>
+      <c r="G146" s="96" t="n"/>
+      <c r="H146" s="96" t="n"/>
+      <c r="I146" s="96" t="n"/>
+      <c r="J146" s="96" t="n"/>
+      <c r="K146" s="96" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="96" t="n"/>
+      <c r="B147" s="96" t="n"/>
+      <c r="C147" s="96" t="n"/>
+      <c r="D147" s="96" t="n"/>
+      <c r="E147" s="96" t="n"/>
+      <c r="F147" s="96" t="n"/>
+      <c r="G147" s="96" t="n"/>
+      <c r="H147" s="96" t="n"/>
+      <c r="I147" s="96" t="n"/>
+      <c r="J147" s="96" t="n"/>
+      <c r="K147" s="96" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="96" t="n"/>
+      <c r="B148" s="96" t="n"/>
+      <c r="C148" s="96" t="n"/>
+      <c r="D148" s="96" t="n"/>
+      <c r="E148" s="96" t="n"/>
+      <c r="F148" s="96" t="n"/>
+      <c r="G148" s="96" t="n"/>
+      <c r="H148" s="96" t="n"/>
+      <c r="I148" s="96" t="n"/>
+      <c r="J148" s="96" t="n"/>
+      <c r="K148" s="96" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="96" t="n"/>
+      <c r="B149" s="96" t="n"/>
+      <c r="C149" s="96" t="n"/>
+      <c r="D149" s="96" t="n"/>
+      <c r="E149" s="96" t="n"/>
+      <c r="F149" s="96" t="n"/>
+      <c r="G149" s="96" t="n"/>
+      <c r="H149" s="96" t="n"/>
+      <c r="I149" s="96" t="n"/>
+      <c r="J149" s="96" t="n"/>
+      <c r="K149" s="96" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="96" t="n"/>
+      <c r="B150" s="96" t="n"/>
+      <c r="C150" s="96" t="n"/>
+      <c r="D150" s="96" t="n"/>
+      <c r="E150" s="96" t="n"/>
+      <c r="F150" s="96" t="n"/>
+      <c r="G150" s="96" t="n"/>
+      <c r="H150" s="96" t="n"/>
+      <c r="I150" s="96" t="n"/>
+      <c r="J150" s="96" t="n"/>
+      <c r="K150" s="96" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="96" t="n"/>
+      <c r="B151" s="96" t="n"/>
+      <c r="C151" s="96" t="n"/>
+      <c r="D151" s="96" t="n"/>
+      <c r="E151" s="96" t="n"/>
+      <c r="F151" s="96" t="n"/>
+      <c r="G151" s="96" t="n"/>
+      <c r="H151" s="96" t="n"/>
+      <c r="I151" s="96" t="n"/>
+      <c r="J151" s="96" t="n"/>
+      <c r="K151" s="96" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="96" t="n"/>
+      <c r="B152" s="96" t="n"/>
+      <c r="C152" s="96" t="n"/>
+      <c r="D152" s="96" t="n"/>
+      <c r="E152" s="96" t="n"/>
+      <c r="F152" s="96" t="n"/>
+      <c r="G152" s="96" t="n"/>
+      <c r="H152" s="96" t="n"/>
+      <c r="I152" s="96" t="n"/>
+      <c r="J152" s="96" t="n"/>
+      <c r="K152" s="96" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="96" t="n"/>
+      <c r="B153" s="96" t="n"/>
+      <c r="C153" s="96" t="n"/>
+      <c r="D153" s="96" t="n"/>
+      <c r="E153" s="96" t="n"/>
+      <c r="F153" s="96" t="n"/>
+      <c r="G153" s="96" t="n"/>
+      <c r="H153" s="96" t="n"/>
+      <c r="I153" s="96" t="n"/>
+      <c r="J153" s="96" t="n"/>
+      <c r="K153" s="96" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="96" t="n"/>
+      <c r="B154" s="96" t="n"/>
+      <c r="C154" s="96" t="n"/>
+      <c r="D154" s="96" t="n"/>
+      <c r="E154" s="96" t="n"/>
+      <c r="F154" s="96" t="n"/>
+      <c r="G154" s="96" t="n"/>
+      <c r="H154" s="96" t="n"/>
+      <c r="I154" s="96" t="n"/>
+      <c r="J154" s="96" t="n"/>
+      <c r="K154" s="96" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="96" t="n"/>
+      <c r="B155" s="96" t="n"/>
+      <c r="C155" s="96" t="n"/>
+      <c r="D155" s="96" t="n"/>
+      <c r="E155" s="96" t="n"/>
+      <c r="F155" s="96" t="n"/>
+      <c r="G155" s="96" t="n"/>
+      <c r="H155" s="96" t="n"/>
+      <c r="I155" s="96" t="n"/>
+      <c r="J155" s="96" t="n"/>
+      <c r="K155" s="96" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="96" t="n"/>
+      <c r="B156" s="96" t="n"/>
+      <c r="C156" s="96" t="n"/>
+      <c r="D156" s="96" t="n"/>
+      <c r="E156" s="96" t="n"/>
+      <c r="F156" s="96" t="n"/>
+      <c r="G156" s="96" t="n"/>
+      <c r="H156" s="96" t="n"/>
+      <c r="I156" s="96" t="n"/>
+      <c r="J156" s="96" t="n"/>
+      <c r="K156" s="96" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="96" t="n"/>
+      <c r="B157" s="96" t="n"/>
+      <c r="C157" s="96" t="n"/>
+      <c r="D157" s="96" t="n"/>
+      <c r="E157" s="96" t="n"/>
+      <c r="F157" s="96" t="n"/>
+      <c r="G157" s="96" t="n"/>
+      <c r="H157" s="96" t="n"/>
+      <c r="I157" s="96" t="n"/>
+      <c r="J157" s="96" t="n"/>
+      <c r="K157" s="96" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="96" t="n"/>
+      <c r="B158" s="96" t="n"/>
+      <c r="C158" s="96" t="n"/>
+      <c r="D158" s="96" t="n"/>
+      <c r="E158" s="96" t="n"/>
+      <c r="F158" s="96" t="n"/>
+      <c r="G158" s="96" t="n"/>
+      <c r="H158" s="96" t="n"/>
+      <c r="I158" s="96" t="n"/>
+      <c r="J158" s="96" t="n"/>
+      <c r="K158" s="96" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="96" t="n"/>
+      <c r="B159" s="96" t="n"/>
+      <c r="C159" s="96" t="n"/>
+      <c r="D159" s="96" t="n"/>
+      <c r="E159" s="96" t="n"/>
+      <c r="F159" s="96" t="n"/>
+      <c r="G159" s="96" t="n"/>
+      <c r="H159" s="96" t="n"/>
+      <c r="I159" s="96" t="n"/>
+      <c r="J159" s="96" t="n"/>
+      <c r="K159" s="96" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:H4"/>
-  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid Product" error="Please select a valid product" promptTitle="Product Selector" prompt="Select a product to view its charts" type="list">
+      <formula1>"iGO,Affirm,InsureSight,DocFast"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -23421,50 +29188,29 @@
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="57" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>Keystone BenefitTech, Inc.</t>
         </is>
       </c>
-      <c r="B1" s="58" t="n"/>
-      <c r="C1" s="58" t="n"/>
-      <c r="D1" s="58" t="n"/>
-      <c r="E1" s="58" t="n"/>
-      <c r="F1" s="58" t="n"/>
-      <c r="G1" s="58" t="n"/>
-      <c r="H1" s="58" t="n"/>
       <c r="I1" s="59" t="n"/>
       <c r="J1" s="59" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="60" t="inlineStr">
+      <c r="A2" s="85" t="inlineStr">
         <is>
           <t>P&amp;L Reporting &amp; Allocation Model — FY2025</t>
         </is>
       </c>
-      <c r="B2" s="58" t="n"/>
-      <c r="C2" s="58" t="n"/>
-      <c r="D2" s="58" t="n"/>
-      <c r="E2" s="58" t="n"/>
-      <c r="F2" s="58" t="n"/>
-      <c r="G2" s="58" t="n"/>
-      <c r="H2" s="58" t="n"/>
       <c r="I2" s="59" t="n"/>
       <c r="J2" s="59" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="61" t="inlineStr">
+      <c r="A3" s="86" t="inlineStr">
         <is>
           <t>Last Updated: 2026-02-28</t>
         </is>
       </c>
-      <c r="B3" s="58" t="n"/>
-      <c r="C3" s="58" t="n"/>
-      <c r="D3" s="58" t="n"/>
-      <c r="E3" s="58" t="n"/>
-      <c r="F3" s="58" t="n"/>
-      <c r="G3" s="58" t="n"/>
-      <c r="H3" s="58" t="n"/>
       <c r="I3" s="59" t="n"/>
       <c r="J3" s="59" t="n"/>
     </row>
@@ -23486,6 +29232,13 @@
           <t>EXECUTIVE SUMMARY</t>
         </is>
       </c>
+      <c r="B5" s="87" t="n"/>
+      <c r="C5" s="87" t="n"/>
+      <c r="D5" s="87" t="n"/>
+      <c r="E5" s="87" t="n"/>
+      <c r="F5" s="87" t="n"/>
+      <c r="G5" s="87" t="n"/>
+      <c r="H5" s="87" t="n"/>
       <c r="I5" s="59" t="n"/>
       <c r="J5" s="59" t="n"/>
     </row>
@@ -23508,19 +29261,19 @@
           <t>FULL YEAR REVENUE</t>
         </is>
       </c>
-      <c r="C7" s="65" t="n"/>
+      <c r="C7" s="88" t="n"/>
       <c r="D7" s="66" t="inlineStr">
         <is>
           <t>CONTRIBUTION MARGIN %</t>
         </is>
       </c>
-      <c r="E7" s="67" t="n"/>
+      <c r="E7" s="88" t="n"/>
       <c r="F7" s="64" t="inlineStr">
         <is>
           <t>TOP PRODUCT BY REVENUE</t>
         </is>
       </c>
-      <c r="G7" s="65" t="n"/>
+      <c r="G7" s="88" t="n"/>
       <c r="H7" s="59" t="n"/>
       <c r="I7" s="59" t="n"/>
       <c r="J7" s="59" t="n"/>
@@ -23531,18 +29284,18 @@
         <f>'P&amp;L - Monthly Trend'!R7</f>
         <v/>
       </c>
-      <c r="C8" s="65" t="n"/>
+      <c r="C8" s="88" t="n"/>
       <c r="D8" s="69">
         <f>'P&amp;L - Monthly Trend'!R10</f>
         <v/>
       </c>
-      <c r="E8" s="67" t="n"/>
+      <c r="E8" s="88" t="n"/>
       <c r="F8" s="70" t="inlineStr">
         <is>
           <t>iGO</t>
         </is>
       </c>
-      <c r="G8" s="65" t="n"/>
+      <c r="G8" s="88" t="n"/>
       <c r="H8" s="59" t="n"/>
       <c r="I8" s="59" t="n"/>
       <c r="J8" s="59" t="n"/>
@@ -23566,19 +29319,19 @@
           <t>BEST MONTH (REVENUE)</t>
         </is>
       </c>
-      <c r="C10" s="67" t="n"/>
+      <c r="C10" s="88" t="n"/>
       <c r="D10" s="64" t="inlineStr">
         <is>
           <t>TOTAL COST OF REVENUE</t>
         </is>
       </c>
-      <c r="E10" s="65" t="n"/>
+      <c r="E10" s="88" t="n"/>
       <c r="F10" s="66" t="inlineStr">
         <is>
           <t>Q4 vs Q1 REVENUE GROWTH</t>
         </is>
       </c>
-      <c r="G10" s="67" t="n"/>
+      <c r="G10" s="88" t="n"/>
       <c r="H10" s="59" t="n"/>
       <c r="I10" s="59" t="n"/>
       <c r="J10" s="59" t="n"/>
@@ -23590,24 +29343,28 @@
           <t>December</t>
         </is>
       </c>
-      <c r="C11" s="67" t="n"/>
+      <c r="C11" s="88" t="n"/>
       <c r="D11" s="68">
         <f>'P&amp;L - Monthly Trend'!R8</f>
         <v/>
       </c>
-      <c r="E11" s="65" t="n"/>
+      <c r="E11" s="88" t="n"/>
       <c r="F11" s="69">
         <f>('P&amp;L - Monthly Trend'!Q7-'P&amp;L - Monthly Trend'!N7)/'P&amp;L - Monthly Trend'!N7</f>
         <v/>
       </c>
-      <c r="G11" s="67" t="n"/>
+      <c r="G11" s="88" t="n"/>
       <c r="H11" s="59" t="n"/>
       <c r="I11" s="59" t="n"/>
       <c r="J11" s="59" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="59" t="n"/>
-      <c r="B12" s="59" t="n"/>
+      <c r="B12" s="59" t="inlineStr">
+        <is>
+          <t>file:///C:\Users\connor.atlee\Downloads\KeystoneBenefitTech_PL_Model.xlsx</t>
+        </is>
+      </c>
       <c r="C12" s="59" t="n"/>
       <c r="D12" s="59" t="n"/>
       <c r="E12" s="59" t="n"/>
@@ -23624,13 +29381,22 @@
           <t>TABLE OF CONTENTS</t>
         </is>
       </c>
+      <c r="C13" s="87" t="n"/>
+      <c r="D13" s="87" t="n"/>
+      <c r="E13" s="87" t="n"/>
+      <c r="F13" s="87" t="n"/>
+      <c r="G13" s="87" t="n"/>
       <c r="H13" s="59" t="n"/>
       <c r="I13" s="59" t="n"/>
       <c r="J13" s="59" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="59" t="n"/>
-      <c r="B14" s="59" t="n"/>
+      <c r="B14" s="59" t="inlineStr">
+        <is>
+          <t>file:///C:\Users\connor.atlee\Downloads\KeystoneBenefitTech_PL_Model.xlsx</t>
+        </is>
+      </c>
       <c r="C14" s="59" t="n"/>
       <c r="D14" s="59" t="n"/>
       <c r="E14" s="59" t="n"/>
@@ -23826,22 +29592,22 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="D8:E8"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="F11:G11"/>
+    <mergeCell ref="D10:E10"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D10:E10"/>
     <mergeCell ref="F10:G10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B13:G13"/>
-    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="F7:G7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B8:C8"/>
     <mergeCell ref="F8:G8"/>
   </mergeCells>
   <hyperlinks>
@@ -23917,7 +29683,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -26535,7 +32300,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -31323,7 +37087,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
@@ -39430,7 +45193,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
